--- a/scaling_experiment/figure_source_data.xlsx
+++ b/scaling_experiment/figure_source_data.xlsx
@@ -499,16 +499,16 @@
         <v>11800</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.885 ± 0.003</t>
+          <t>0.882 ± 0.005</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.916 ± 0.002</t>
+          <t>0.915 ± 0.002</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>196.9 ± 5.4</t>
+          <t>197.8 ± 4.6</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7.7 ± 0.5</t>
+          <t>8.1 ± 1.2</t>
         </is>
       </c>
     </row>
@@ -555,51 +555,51 @@
         <v>23600</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.916 ± 0.004</t>
+          <t>0.915 ± 0.004</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>0.934 ± 0.003</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.924 ± 0.003</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.993 ± 0.000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.967 ± 0.002</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.828 ± 0.005</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>0.935 ± 0.002</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.925 ± 0.002</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.993 ± 0.000</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.966 ± 0.001</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.827 ± 0.006</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.934 ± 0.002</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>126.9 ± 24.5</t>
+          <t>129.6 ± 20.8</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>9.4 ± 1.6</t>
+          <t>9.6 ± 1.6</t>
         </is>
       </c>
     </row>
@@ -611,36 +611,36 @@
         <v>35400</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.919 ± 0.012</t>
+          <t>0.919 ± 0.010</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.939 ± 0.004</t>
+          <t>0.938 ± 0.004</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.930 ± 0.004</t>
+          <t>0.929 ± 0.005</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.995 ± 0.000</t>
+          <t>0.995 ± 0.001</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.974 ± 0.003</t>
+          <t>0.973 ± 0.003</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.832 ± 0.005</t>
+          <t>0.832 ± 0.004</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>110.9 ± 20.5</t>
+          <t>107.2 ± 18.3</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>11.3 ± 1.5</t>
+          <t>11.2 ± 1.3</t>
         </is>
       </c>
     </row>
@@ -667,36 +667,36 @@
         <v>47200</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.922 ± 0.006</t>
+          <t>0.924 ± 0.006</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.942 ± 0.003</t>
+          <t>0.944 ± 0.004</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.933 ± 0.004</t>
+          <t>0.935 ± 0.005</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.994 ± 0.001</t>
+          <t>0.995 ± 0.001</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.974 ± 0.003</t>
+          <t>0.976 ± 0.004</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.835 ± 0.003</t>
+          <t>0.836 ± 0.004</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -706,12 +706,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>86.3 ± 12.6</t>
+          <t>89.2 ± 11.5</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>12.2 ± 1.8</t>
+          <t>12.6 ± 1.8</t>
         </is>
       </c>
     </row>
@@ -723,21 +723,21 @@
         <v>59000</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.939 ± 0.008</t>
+          <t>0.938 ± 0.007</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.951 ± 0.006</t>
+          <t>0.951 ± 0.005</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.944 ± 0.007</t>
+          <t>0.944 ± 0.006</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.981 ± 0.004</t>
+          <t>0.981 ± 0.003</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>76.9 ± 8.8</t>
+          <t>77.0 ± 8.0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>12.7 ± 0.8</t>
+          <t>13.5 ± 1.7</t>
         </is>
       </c>
     </row>
@@ -779,11 +779,11 @@
         <v>70800</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.942 ± 0.003</t>
+          <t>0.942 ± 0.004</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.946 ± 0.004</t>
+          <t>0.946 ± 0.003</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.842 ± 0.002</t>
+          <t>0.841 ± 0.002</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>72.3 ± 5.1</t>
+          <t>71.6 ± 4.7</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>14.1 ± 0.9</t>
+          <t>14.7 ± 1.9</t>
         </is>
       </c>
     </row>
@@ -835,11 +835,11 @@
         <v>82600</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.944 ± 0.003</t>
+          <t>0.944 ± 0.004</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.947 ± 0.004</t>
+          <t>0.947 ± 0.003</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -864,22 +864,22 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.839 ± 0.002</t>
+          <t>0.840 ± 0.003</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.940 ± 0.001</t>
+          <t>0.940 ± 0.002</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>60.0 ± 7.2</t>
+          <t>61.1 ± 8.1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>14.3 ± 1.2</t>
+          <t>15.2 ± 1.8</t>
         </is>
       </c>
     </row>
@@ -891,21 +891,21 @@
         <v>94400</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.944 ± 0.007</t>
+          <t>0.947 ± 0.007</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.955 ± 0.003</t>
+          <t>0.956 ± 0.003</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.948 ± 0.004</t>
+          <t>0.949 ± 0.003</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>57.6 ± 8.0</t>
+          <t>57.0 ± 6.7</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16.0 ± 1.7</t>
+          <t>16.6 ± 1.9</t>
         </is>
       </c>
     </row>
@@ -947,21 +947,21 @@
         <v>106200</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.952 ± 0.004</t>
+          <t>0.951 ± 0.005</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.960 ± 0.004</t>
+          <t>0.959 ± 0.003</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.954 ± 0.005</t>
+          <t>0.953 ± 0.004</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -971,27 +971,27 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.986 ± 0.001</t>
+          <t>0.985 ± 0.001</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.841 ± 0.003</t>
+          <t>0.840 ± 0.003</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.941 ± 0.002</t>
+          <t>0.940 ± 0.002</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>51.0 ± 4.2</t>
+          <t>52.2 ± 4.7</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>15.7 ± 1.1</t>
+          <t>16.6 ± 1.6</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
         <v>118000</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.958 ± 0.002</t>
+          <t>0.959 ± 0.003</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.952 ± 0.003</t>
+          <t>0.953 ± 0.003</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.839 ± 0.001</t>
+          <t>0.840 ± 0.001</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>49.0 ± 4.2</t>
+          <t>48.4 ± 3.6</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>16.9 ± 1.5</t>
+          <t>17.0 ± 1.4</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R69"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1551,170 +1551,170 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>23600</v>
+        <v>11800</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9157753778048124</v>
+        <v>0.8784376009152353</v>
       </c>
       <c r="E9" t="n">
-        <v>0.936534563694568</v>
+        <v>0.9137065322442168</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9269747865905574</v>
+        <v>0.9005486216692881</v>
       </c>
       <c r="G9" t="n">
-        <v>0.993582456167003</v>
+        <v>0.9903411215221872</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9678223701395112</v>
+        <v>0.9531375519094936</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7575102589931</v>
+        <v>0.7613307716619675</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8673148132095528</v>
+        <v>0.8591044842637422</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8280244458707778</v>
+        <v>0.8169011435575534</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9344042535622964</v>
+        <v>0.9290279428472116</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6495180102534073</v>
+        <v>0.6460455569733953</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8049430300475015</v>
+        <v>0.8017161849344926</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7274356419862167</v>
+        <v>0.7169116865270058</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8168497976800012</v>
+        <v>0.814532101702371</v>
       </c>
       <c r="Q9" t="n">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="R9" t="n">
-        <v>8.933333333333334</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>23600</v>
+        <v>11800</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9098781018226578</v>
+        <v>0.8743598110204671</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9355152243030856</v>
+        <v>0.9150414616353812</v>
       </c>
       <c r="F10" t="n">
-        <v>0.926175639105243</v>
+        <v>0.90209089781479</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9935230663662696</v>
+        <v>0.9906034309682054</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9664230814608558</v>
+        <v>0.9536247293000976</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7345893892225406</v>
+        <v>0.6994427507867996</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8642844607262672</v>
+        <v>0.8609208561352528</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8174006503961886</v>
+        <v>0.8165568515165833</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9312708581793212</v>
+        <v>0.9290118857766988</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6444464629808524</v>
+        <v>0.6447171034945306</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7974969266264454</v>
+        <v>0.7956790697237742</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7212652044336698</v>
+        <v>0.7210295096977063</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8100102994854959</v>
+        <v>0.8074521499559668</v>
       </c>
       <c r="Q10" t="n">
-        <v>104</v>
+        <v>200</v>
       </c>
       <c r="R10" t="n">
-        <v>8.166666666666666</v>
+        <v>10.96666666666667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>23600</v>
+        <v>11800</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9160264011589938</v>
+        <v>0.8757364405703391</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9380159874327648</v>
+        <v>0.9152766909058088</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9286854630477492</v>
+        <v>0.9020047152433832</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9938738958208166</v>
+        <v>0.9901748953484116</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9673526828061276</v>
+        <v>0.9527840679168502</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7411552184691477</v>
+        <v>0.7129794526031806</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8667313483721381</v>
+        <v>0.8619601781134194</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8270601530477992</v>
+        <v>0.8169201472749886</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9340781521858332</v>
+        <v>0.929555879895568</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6550363318033824</v>
+        <v>0.6438142125438874</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8029486521478247</v>
+        <v>0.799332467618646</v>
       </c>
       <c r="O11" t="n">
-        <v>0.730502415085385</v>
+        <v>0.7201975642127072</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8133716624309889</v>
+        <v>0.8123051094494858</v>
       </c>
       <c r="Q11" t="n">
-        <v>122</v>
+        <v>200</v>
       </c>
       <c r="R11" t="n">
-        <v>8.449999999999999</v>
+        <v>8.733333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -1725,52 +1725,52 @@
         <v>23600</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9130934158356842</v>
+        <v>0.9157753778048124</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9330596829083004</v>
+        <v>0.936534563694568</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9230013899217868</v>
+        <v>0.9269747865905574</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9933545334018266</v>
+        <v>0.993582456167003</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9660312208815972</v>
+        <v>0.9678223701395112</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7454027084656172</v>
+        <v>0.7575102589931</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8656624809429079</v>
+        <v>0.8673148132095528</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8240780897403959</v>
+        <v>0.8280244458707778</v>
       </c>
       <c r="L12" t="n">
-        <v>0.933438261984858</v>
+        <v>0.9344042535622964</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6493507811092936</v>
+        <v>0.6495180102534073</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8034678992711888</v>
+        <v>0.8049430300475015</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7260695646994426</v>
+        <v>0.7274356419862167</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8155888139335824</v>
+        <v>0.8168497976800012</v>
       </c>
       <c r="Q12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R12" t="n">
-        <v>9.15</v>
+        <v>8.933333333333334</v>
       </c>
     </row>
     <row r="13">
@@ -1781,52 +1781,52 @@
         <v>23600</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9133917875888276</v>
+        <v>0.9098781018226578</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9340593886621434</v>
+        <v>0.9355152243030856</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9241674892713064</v>
+        <v>0.926175639105243</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9929456449917536</v>
+        <v>0.9935230663662696</v>
       </c>
       <c r="H13" t="n">
-        <v>0.964745428286651</v>
+        <v>0.9664230814608558</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7108113320343524</v>
+        <v>0.7345893892225406</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8656598230822441</v>
+        <v>0.8642844607262672</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8234414510221464</v>
+        <v>0.8174006503961886</v>
       </c>
       <c r="L13" t="n">
-        <v>0.932472711038815</v>
+        <v>0.9312708581793212</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6498070101996284</v>
+        <v>0.6444464629808524</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8000896101124694</v>
+        <v>0.7974969266264454</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7271783752036207</v>
+        <v>0.7212652044336698</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8114749618350688</v>
+        <v>0.8100102994854959</v>
       </c>
       <c r="Q13" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="R13" t="n">
-        <v>8.416666666666666</v>
+        <v>8.166666666666666</v>
       </c>
     </row>
     <row r="14">
@@ -1837,52 +1837,52 @@
         <v>23600</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9224390200299722</v>
+        <v>0.9160264011589938</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9361993463331774</v>
+        <v>0.9380159874327648</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9265495728976616</v>
+        <v>0.9286854630477492</v>
       </c>
       <c r="G14" t="n">
-        <v>0.99292205307012</v>
+        <v>0.9938738958208166</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9655922910773262</v>
+        <v>0.9673526828061276</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7512669782916965</v>
+        <v>0.7411552184691477</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8708197147592633</v>
+        <v>0.8667313483721381</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8370391629029913</v>
+        <v>0.8270601530477992</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9385044367770178</v>
+        <v>0.9340781521858332</v>
       </c>
       <c r="M14" t="n">
-        <v>0.652844427801156</v>
+        <v>0.6550363318033824</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8092402338805592</v>
+        <v>0.8029486521478247</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7329421203757072</v>
+        <v>0.730502415085385</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8216814671724001</v>
+        <v>0.8133716624309889</v>
       </c>
       <c r="Q14" t="n">
-        <v>179</v>
+        <v>122</v>
       </c>
       <c r="R14" t="n">
-        <v>12.81666666666667</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1893,388 +1893,388 @@
         <v>23600</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9201323242481976</v>
+        <v>0.9130934158356842</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9322740601064196</v>
+        <v>0.9330596829083004</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9218279892429252</v>
+        <v>0.9230013899217868</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9936170378443996</v>
+        <v>0.9933545334018266</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9674837473773944</v>
+        <v>0.9660312208815972</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7248715170855118</v>
+        <v>0.7454027084656172</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8681280994710237</v>
+        <v>0.8656624809429079</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8290512048945493</v>
+        <v>0.8240780897403959</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9352279427617588</v>
+        <v>0.933438261984858</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6511809011796628</v>
+        <v>0.6493507811092936</v>
       </c>
       <c r="N15" t="n">
-        <v>0.804291126967481</v>
+        <v>0.8034678992711888</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7303549111512768</v>
+        <v>0.7260695646994426</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8165084255958761</v>
+        <v>0.8155888139335824</v>
       </c>
       <c r="Q15" t="n">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="R15" t="n">
-        <v>9.85</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B16" t="n">
-        <v>35400</v>
+        <v>23600</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9155009772297672</v>
+        <v>0.9133917875888276</v>
       </c>
       <c r="E16" t="n">
-        <v>0.939852334134302</v>
+        <v>0.9340593886621434</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9304806034008</v>
+        <v>0.9241674892713064</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9950712553420762</v>
+        <v>0.9929456449917536</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9738068769842224</v>
+        <v>0.964745428286651</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7335172223570613</v>
+        <v>0.7108113320343524</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8686491900520751</v>
+        <v>0.8656598230822441</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8272511808190166</v>
+        <v>0.8234414510221464</v>
       </c>
       <c r="L16" t="n">
-        <v>0.935197228098689</v>
+        <v>0.932472711038815</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6485815920743526</v>
+        <v>0.6498070101996284</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8023602368032712</v>
+        <v>0.8000896101124694</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7286541084603542</v>
+        <v>0.7271783752036207</v>
       </c>
       <c r="P16" t="n">
-        <v>0.814484413254304</v>
+        <v>0.8114749618350688</v>
       </c>
       <c r="Q16" t="n">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="R16" t="n">
-        <v>10.26666666666667</v>
+        <v>8.416666666666666</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n">
-        <v>35400</v>
+        <v>23600</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9058158528720188</v>
+        <v>0.9224390200299722</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9348665682631372</v>
+        <v>0.9361993463331774</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9246201384070516</v>
+        <v>0.9265495728976616</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9951168486865322</v>
+        <v>0.99292205307012</v>
       </c>
       <c r="H17" t="n">
-        <v>0.971446682532624</v>
+        <v>0.9655922910773262</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7458556520766434</v>
+        <v>0.7512669782916965</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8715900659163042</v>
+        <v>0.8708197147592633</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8356304999469045</v>
+        <v>0.8370391629029913</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9392324042774836</v>
+        <v>0.9385044367770178</v>
       </c>
       <c r="M17" t="n">
-        <v>0.653529891652745</v>
+        <v>0.652844427801156</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8084329814956857</v>
+        <v>0.8092402338805592</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7369230266676035</v>
+        <v>0.7329421203757072</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8190932625931704</v>
+        <v>0.8216814671724001</v>
       </c>
       <c r="Q17" t="n">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="R17" t="n">
-        <v>14.06666666666667</v>
+        <v>12.81666666666667</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n">
-        <v>35400</v>
+        <v>23600</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>0.932313868630382</v>
+        <v>0.9201323242481976</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9440736879580852</v>
+        <v>0.9322740601064196</v>
       </c>
       <c r="F18" t="n">
-        <v>0.935546265843624</v>
+        <v>0.9218279892429252</v>
       </c>
       <c r="G18" t="n">
-        <v>0.994886117494041</v>
+        <v>0.9936170378443996</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9759969651667912</v>
+        <v>0.9674837473773944</v>
       </c>
       <c r="I18" t="n">
-        <v>0.739057069750376</v>
+        <v>0.7248715170855118</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8684972974184384</v>
+        <v>0.8681280994710237</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8329850100640426</v>
+        <v>0.8290512048945493</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9359937964405236</v>
+        <v>0.9352279427617588</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6570065359589893</v>
+        <v>0.6511809011796628</v>
       </c>
       <c r="N18" t="n">
-        <v>0.807323788126336</v>
+        <v>0.804291126967481</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7320226030957436</v>
+        <v>0.7303549111512768</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8183936328712726</v>
+        <v>0.8165084255958761</v>
       </c>
       <c r="Q18" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="R18" t="n">
-        <v>10.85</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>35400</v>
+        <v>23600</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9254171843616832</v>
+        <v>0.915589776899298</v>
       </c>
       <c r="E19" t="n">
-        <v>0.942641352077892</v>
+        <v>0.9311401142025366</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9342180777851384</v>
+        <v>0.920411439031497</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9951966792146164</v>
+        <v>0.9938958883539808</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9756635308450016</v>
+        <v>0.96794009737783</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7388585171638372</v>
+        <v>0.7294539088271975</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8718946389424624</v>
+        <v>0.8687946607872662</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8377640560735545</v>
+        <v>0.8285028889132321</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9393997216552912</v>
+        <v>0.9352114239797036</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6596383315132273</v>
+        <v>0.6464524314798689</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8067360831627725</v>
+        <v>0.803596235769624</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7379719743314184</v>
+        <v>0.7278815942687508</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8172637769205049</v>
+        <v>0.8161146967049552</v>
       </c>
       <c r="Q19" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="R19" t="n">
-        <v>10.75</v>
+        <v>8.766666666666667</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B20" t="n">
-        <v>35400</v>
+        <v>23600</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9298555362396452</v>
+        <v>0.9086677447941776</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9404925957928022</v>
+        <v>0.9301996909700878</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9316571738679654</v>
+        <v>0.9198334386789516</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9954396889087728</v>
+        <v>0.9931345437481072</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9759548035044578</v>
+        <v>0.9637477029308376</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7721584238792254</v>
+        <v>0.7475927615619805</v>
       </c>
       <c r="J20" t="n">
-        <v>0.871547919282979</v>
+        <v>0.8675672858829088</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8381840149067903</v>
+        <v>0.8285619300260667</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9401216987726276</v>
+        <v>0.9358632216330558</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6646337601051325</v>
+        <v>0.6581925930145452</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8091565919123999</v>
+        <v>0.8028771197376811</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7411690048648236</v>
+        <v>0.7341755002839495</v>
       </c>
       <c r="P20" t="n">
-        <v>0.81930212422879</v>
+        <v>0.8135840765282539</v>
       </c>
       <c r="Q20" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="R20" t="n">
-        <v>12.6</v>
+        <v>11.86666666666667</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>35400</v>
+        <v>23600</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9021616243812464</v>
+        <v>0.9148930720616072</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9339744382245364</v>
+        <v>0.9363117268001148</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9247266735783296</v>
+        <v>0.926980523595418</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9940293050911798</v>
+        <v>0.9940082345153548</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9688286722712856</v>
+        <v>0.9690155791035736</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7325705353957522</v>
+        <v>0.7314917742086323</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8680777088945222</v>
+        <v>0.8698700277234982</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8265164137038297</v>
+        <v>0.8321320007776338</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9344461694886944</v>
+        <v>0.9364458956644672</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6460810977901588</v>
+        <v>0.6528570606345737</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7997587779586757</v>
+        <v>0.8053743705884361</v>
       </c>
       <c r="O21" t="n">
-        <v>0.726919575590699</v>
+        <v>0.7319292115286029</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8106479712469946</v>
+        <v>0.8165679637908251</v>
       </c>
       <c r="Q21" t="n">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="R21" t="n">
-        <v>9.983333333333333</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="22">
@@ -2285,2345 +2285,2345 @@
         <v>35400</v>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9212209182864716</v>
+        <v>0.9155009772297672</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9393441307119028</v>
+        <v>0.939852334134302</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9303559675000574</v>
+        <v>0.9304806034008</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9950340571933464</v>
+        <v>0.9950712553420762</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9732858987994796</v>
+        <v>0.9738068769842224</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7112289476004425</v>
+        <v>0.7335172223570613</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8688532554075573</v>
+        <v>0.8686491900520751</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8289753387726064</v>
+        <v>0.8272511808190166</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9355984427046508</v>
+        <v>0.935197228098689</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6511858090229398</v>
+        <v>0.6485815920743526</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8019323066985355</v>
+        <v>0.8023602368032712</v>
       </c>
       <c r="O22" t="n">
-        <v>0.730924773200484</v>
+        <v>0.7286541084603542</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8124846801626728</v>
+        <v>0.814484413254304</v>
       </c>
       <c r="Q22" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="R22" t="n">
-        <v>10.35</v>
+        <v>10.26666666666667</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B23" t="n">
-        <v>47200</v>
+        <v>35400</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>0.924757537217994</v>
+        <v>0.9058158528720188</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9465667985485688</v>
+        <v>0.9348665682631372</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9386828850048428</v>
+        <v>0.9246201384070516</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9950854472725462</v>
+        <v>0.9951168486865322</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9759983022948244</v>
+        <v>0.971446682532624</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7406921836973455</v>
+        <v>0.7458556520766434</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8719034287760556</v>
+        <v>0.8715900659163042</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8362098708888175</v>
+        <v>0.8356304999469045</v>
       </c>
       <c r="L23" t="n">
-        <v>0.939244555455062</v>
+        <v>0.9392324042774836</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6574950924137422</v>
+        <v>0.653529891652745</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8073996329943721</v>
+        <v>0.8084329814956857</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7396152803470433</v>
+        <v>0.7369230266676035</v>
       </c>
       <c r="P23" t="n">
-        <v>0.8183217787095302</v>
+        <v>0.8190932625931704</v>
       </c>
       <c r="Q23" t="n">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="R23" t="n">
-        <v>11.25</v>
+        <v>14.06666666666667</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B24" t="n">
-        <v>47200</v>
+        <v>35400</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.91499837352305</v>
+        <v>0.932313868630382</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9443957841542092</v>
+        <v>0.9440736879580852</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9363009297513308</v>
+        <v>0.935546265843624</v>
       </c>
       <c r="G24" t="n">
-        <v>0.995143869553</v>
+        <v>0.994886117494041</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9779069566856884</v>
+        <v>0.9759969651667912</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7585311506781318</v>
+        <v>0.739057069750376</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8683540968607</v>
+        <v>0.8684972974184384</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8303880076365838</v>
+        <v>0.8329850100640426</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9352741500562384</v>
+        <v>0.9359937964405236</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6454076221896743</v>
+        <v>0.6570065359589893</v>
       </c>
       <c r="N24" t="n">
-        <v>0.8091125688418771</v>
+        <v>0.807323788126336</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7288636588806627</v>
+        <v>0.7320226030957436</v>
       </c>
       <c r="P24" t="n">
-        <v>0.8217254506314615</v>
+        <v>0.8183936328712726</v>
       </c>
       <c r="Q24" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="R24" t="n">
-        <v>9.883333333333333</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>47200</v>
+        <v>35400</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9214928335458578</v>
+        <v>0.9254171843616832</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9387989182923244</v>
+        <v>0.942641352077892</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9293000342113265</v>
+        <v>0.9342180777851384</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9935593704781454</v>
+        <v>0.9951966792146164</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9717857098217548</v>
+        <v>0.9756635308450016</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7513817217496934</v>
+        <v>0.7388585171638372</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8708373616535015</v>
+        <v>0.8718946389424624</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8361316309773071</v>
+        <v>0.8377640560735545</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9381469965322676</v>
+        <v>0.9393997216552912</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6527152412064782</v>
+        <v>0.6596383315132273</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8064442672934119</v>
+        <v>0.8067360831627725</v>
       </c>
       <c r="O25" t="n">
-        <v>0.7342577407565002</v>
+        <v>0.7379719743314184</v>
       </c>
       <c r="P25" t="n">
-        <v>0.8169573552625808</v>
+        <v>0.8172637769205049</v>
       </c>
       <c r="Q25" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="R25" t="n">
-        <v>13.91666666666667</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B26" t="n">
-        <v>47200</v>
+        <v>35400</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9274627312690286</v>
+        <v>0.9298555362396452</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9411340847870816</v>
+        <v>0.9404925957928022</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9313883636113914</v>
+        <v>0.9316571738679654</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9939523870949624</v>
+        <v>0.9954396889087728</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9754384042224972</v>
+        <v>0.9759548035044578</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7496988236598255</v>
+        <v>0.7721584238792254</v>
       </c>
       <c r="J26" t="n">
-        <v>0.872384777801358</v>
+        <v>0.871547919282979</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8362763894462937</v>
+        <v>0.8381840149067903</v>
       </c>
       <c r="L26" t="n">
-        <v>0.9389125994972108</v>
+        <v>0.9401216987726276</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6562655425666364</v>
+        <v>0.6646337601051325</v>
       </c>
       <c r="N26" t="n">
-        <v>0.803263109415122</v>
+        <v>0.8091565919123999</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7381683564031298</v>
+        <v>0.7411690048648236</v>
       </c>
       <c r="P26" t="n">
-        <v>0.81335269063799</v>
+        <v>0.81930212422879</v>
       </c>
       <c r="Q26" t="n">
-        <v>85</v>
+        <v>132</v>
       </c>
       <c r="R26" t="n">
-        <v>12.65</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n">
-        <v>47200</v>
+        <v>35400</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>0.92984721216669</v>
+        <v>0.9021616243812464</v>
       </c>
       <c r="E27" t="n">
-        <v>0.943696710943188</v>
+        <v>0.9339744382245364</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9340556989457064</v>
+        <v>0.9247266735783296</v>
       </c>
       <c r="G27" t="n">
-        <v>0.99485287839326</v>
+        <v>0.9940293050911798</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9767116685991836</v>
+        <v>0.9688286722712856</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7397020484446482</v>
+        <v>0.7325705353957522</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8691888880805203</v>
+        <v>0.8680777088945222</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8359693845540228</v>
+        <v>0.8265164137038297</v>
       </c>
       <c r="L27" t="n">
-        <v>0.9374335582126658</v>
+        <v>0.9344461694886944</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6620310579283838</v>
+        <v>0.6460810977901588</v>
       </c>
       <c r="N27" t="n">
-        <v>0.8044424004118219</v>
+        <v>0.7997587779586757</v>
       </c>
       <c r="O27" t="n">
-        <v>0.7391068456697933</v>
+        <v>0.726919575590699</v>
       </c>
       <c r="P27" t="n">
-        <v>0.8146765167844232</v>
+        <v>0.8106479712469946</v>
       </c>
       <c r="Q27" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="R27" t="n">
-        <v>10.81666666666667</v>
+        <v>9.983333333333333</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n">
-        <v>47200</v>
+        <v>35400</v>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9146724907948376</v>
+        <v>0.9212209182864716</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9419665936197096</v>
+        <v>0.9393441307119028</v>
       </c>
       <c r="F28" t="n">
-        <v>0.93363427281136</v>
+        <v>0.9303559675000574</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9944012291697076</v>
+        <v>0.9950340571933464</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9726987735213668</v>
+        <v>0.9732858987994796</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6933435229687333</v>
+        <v>0.7112289476004425</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8691289914849443</v>
+        <v>0.8688532554075573</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8298058678045905</v>
+        <v>0.8289753387726064</v>
       </c>
       <c r="L28" t="n">
-        <v>0.9359241211227798</v>
+        <v>0.9355984427046508</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6499828171443977</v>
+        <v>0.6511858090229398</v>
       </c>
       <c r="N28" t="n">
-        <v>0.800263232135082</v>
+        <v>0.8019323066985355</v>
       </c>
       <c r="O28" t="n">
-        <v>0.7303459012158257</v>
+        <v>0.730924773200484</v>
       </c>
       <c r="P28" t="n">
-        <v>0.8117328105371352</v>
+        <v>0.8124846801626728</v>
       </c>
       <c r="Q28" t="n">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="R28" t="n">
-        <v>11.8</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>47200</v>
+        <v>35400</v>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>0.918064163802092</v>
+        <v>0.915676098367677</v>
       </c>
       <c r="E29" t="n">
-        <v>0.938211042219024</v>
+        <v>0.9313393206887036</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9287821071349718</v>
+        <v>0.9207812698194906</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9929896251742144</v>
+        <v>0.9935239530605668</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9688414449043776</v>
+        <v>0.970393156753076</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7700384226033601</v>
+        <v>0.7517595284943046</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8707536622429328</v>
+        <v>0.8678083681243209</v>
       </c>
       <c r="K29" t="n">
-        <v>0.8368102252754157</v>
+        <v>0.8283448134771603</v>
       </c>
       <c r="L29" t="n">
-        <v>0.9399456963197156</v>
+        <v>0.934853858842948</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6564528852310708</v>
+        <v>0.6487727556749203</v>
       </c>
       <c r="N29" t="n">
-        <v>0.8043689068083948</v>
+        <v>0.8030032625347803</v>
       </c>
       <c r="O29" t="n">
-        <v>0.7377460960026445</v>
+        <v>0.7268427712481249</v>
       </c>
       <c r="P29" t="n">
-        <v>0.8149876056429437</v>
+        <v>0.8150842531384165</v>
       </c>
       <c r="Q29" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="R29" t="n">
-        <v>15.11666666666667</v>
+        <v>10.43333333333333</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B30" t="n">
-        <v>59000</v>
+        <v>35400</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9450822917216352</v>
+        <v>0.9211788365043312</v>
       </c>
       <c r="E30" t="n">
-        <v>0.95368729916892</v>
+        <v>0.9348203877050808</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9467688761017076</v>
+        <v>0.9252271597664888</v>
       </c>
       <c r="G30" t="n">
-        <v>0.997248350724816</v>
+        <v>0.9941786379765593</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9837458558488216</v>
+        <v>0.97080624089187</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7435869768649381</v>
+        <v>0.7151107477139653</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8732929104895372</v>
+        <v>0.8709958687380908</v>
       </c>
       <c r="K30" t="n">
-        <v>0.8425941190681121</v>
+        <v>0.8330650755450993</v>
       </c>
       <c r="L30" t="n">
-        <v>0.9402653682834532</v>
+        <v>0.9378313478741048</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6621792561332547</v>
+        <v>0.648660824138237</v>
       </c>
       <c r="N30" t="n">
-        <v>0.8089306554120294</v>
+        <v>0.807020238622978</v>
       </c>
       <c r="O30" t="n">
-        <v>0.7419770018386795</v>
+        <v>0.7301437939170351</v>
       </c>
       <c r="P30" t="n">
-        <v>0.8193517568898759</v>
+        <v>0.8201775786523164</v>
       </c>
       <c r="Q30" t="n">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="R30" t="n">
-        <v>12.56666666666667</v>
+        <v>11.56666666666667</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>59000</v>
+        <v>35400</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9464379106329192</v>
+        <v>0.9195309561495379</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9544645044911946</v>
+        <v>0.9412180453258008</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9474560794252062</v>
+        <v>0.9325265071414472</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9970289528641032</v>
+        <v>0.9953976311708082</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9837056952216936</v>
+        <v>0.9760501063364772</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7492749628440949</v>
+        <v>0.7369263118852782</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8732689411170007</v>
+        <v>0.8685313878661662</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8416839789049813</v>
+        <v>0.8315732608573819</v>
       </c>
       <c r="L31" t="n">
-        <v>0.9409356097867206</v>
+        <v>0.9359595413704872</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6627889652452797</v>
+        <v>0.653832729048872</v>
       </c>
       <c r="N31" t="n">
-        <v>0.8085982981000351</v>
+        <v>0.8067460215535944</v>
       </c>
       <c r="O31" t="n">
-        <v>0.7409673787705788</v>
+        <v>0.73124362736343</v>
       </c>
       <c r="P31" t="n">
-        <v>0.8185309543026117</v>
+        <v>0.8189103470831093</v>
       </c>
       <c r="Q31" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="R31" t="n">
-        <v>13.05</v>
+        <v>10.68333333333333</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B32" t="n">
-        <v>59000</v>
+        <v>47200</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9403759368069043</v>
+        <v>0.924757537217994</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9527885741541928</v>
+        <v>0.9465667985485688</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9457766502822804</v>
+        <v>0.9386828850048428</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9969758619942594</v>
+        <v>0.9950854472725462</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9820748569553458</v>
+        <v>0.9759983022948244</v>
       </c>
       <c r="I32" t="n">
-        <v>0.764655906773352</v>
+        <v>0.7406921836973455</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8727684165419266</v>
+        <v>0.8719034287760556</v>
       </c>
       <c r="K32" t="n">
-        <v>0.8385335095291163</v>
+        <v>0.8362098708888175</v>
       </c>
       <c r="L32" t="n">
-        <v>0.939575232620489</v>
+        <v>0.939244555455062</v>
       </c>
       <c r="M32" t="n">
-        <v>0.6587903043554871</v>
+        <v>0.6574950924137422</v>
       </c>
       <c r="N32" t="n">
-        <v>0.8078466773089217</v>
+        <v>0.8073996329943721</v>
       </c>
       <c r="O32" t="n">
-        <v>0.7389152677047097</v>
+        <v>0.7396152803470433</v>
       </c>
       <c r="P32" t="n">
-        <v>0.8185382604496779</v>
+        <v>0.8183217787095302</v>
       </c>
       <c r="Q32" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="R32" t="n">
-        <v>12.78333333333333</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B33" t="n">
-        <v>59000</v>
+        <v>47200</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9229081615243822</v>
+        <v>0.91499837352305</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9380432618316792</v>
+        <v>0.9443957841542092</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9287531447120227</v>
+        <v>0.9363009297513308</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9942760696357538</v>
+        <v>0.995143869553</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9726019344435572</v>
+        <v>0.9779069566856884</v>
       </c>
       <c r="I33" t="n">
-        <v>0.743154407698794</v>
+        <v>0.7585311506781318</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8710102913893063</v>
+        <v>0.8683540968607</v>
       </c>
       <c r="K33" t="n">
-        <v>0.8344784355225043</v>
+        <v>0.8303880076365838</v>
       </c>
       <c r="L33" t="n">
-        <v>0.9383955837050448</v>
+        <v>0.9352741500562384</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6475929231450921</v>
+        <v>0.6454076221896743</v>
       </c>
       <c r="N33" t="n">
-        <v>0.8065769274099287</v>
+        <v>0.8091125688418771</v>
       </c>
       <c r="O33" t="n">
-        <v>0.7305660495634267</v>
+        <v>0.7288636588806627</v>
       </c>
       <c r="P33" t="n">
-        <v>0.8186355022673789</v>
+        <v>0.8217254506314615</v>
       </c>
       <c r="Q33" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="R33" t="n">
-        <v>12.71666666666667</v>
+        <v>9.883333333333333</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B34" t="n">
-        <v>59000</v>
+        <v>47200</v>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9422263516710035</v>
+        <v>0.9214928335458578</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9524726690468264</v>
+        <v>0.9387989182923244</v>
       </c>
       <c r="F34" t="n">
-        <v>0.945176136529832</v>
+        <v>0.9293000342113265</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9969995605030968</v>
+        <v>0.9935593704781454</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9819711777839424</v>
+        <v>0.9717857098217548</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7330641098624189</v>
+        <v>0.7513817217496934</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8703361892777384</v>
+        <v>0.8708373616535015</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8350299161376199</v>
+        <v>0.8361316309773071</v>
       </c>
       <c r="L34" t="n">
-        <v>0.9380088743711472</v>
+        <v>0.9381469965322676</v>
       </c>
       <c r="M34" t="n">
-        <v>0.662235000811101</v>
+        <v>0.6527152412064782</v>
       </c>
       <c r="N34" t="n">
-        <v>0.8045592516403307</v>
+        <v>0.8064442672934119</v>
       </c>
       <c r="O34" t="n">
-        <v>0.7377961446805361</v>
+        <v>0.7342577407565002</v>
       </c>
       <c r="P34" t="n">
-        <v>0.8149206140169738</v>
+        <v>0.8169573552625808</v>
       </c>
       <c r="Q34" t="n">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="R34" t="n">
-        <v>11.25</v>
+        <v>13.91666666666667</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B35" t="n">
-        <v>59000</v>
+        <v>47200</v>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>0.936110770714384</v>
+        <v>0.9274627312690286</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9557945174434226</v>
+        <v>0.9411340847870816</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9495095839149756</v>
+        <v>0.9313883636113914</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9972637800168904</v>
+        <v>0.9939523870949624</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9832267630709924</v>
+        <v>0.9754384042224972</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7669494621256233</v>
+        <v>0.7496988236598255</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8732016939501598</v>
+        <v>0.872384777801358</v>
       </c>
       <c r="K35" t="n">
-        <v>0.8401755912550641</v>
+        <v>0.8362763894462937</v>
       </c>
       <c r="L35" t="n">
-        <v>0.9403720773026432</v>
+        <v>0.9389125994972108</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6618220041719367</v>
+        <v>0.6562655425666364</v>
       </c>
       <c r="N35" t="n">
-        <v>0.8068657634093013</v>
+        <v>0.803263109415122</v>
       </c>
       <c r="O35" t="n">
-        <v>0.7411638982703711</v>
+        <v>0.7381683564031298</v>
       </c>
       <c r="P35" t="n">
-        <v>0.8171452938949734</v>
+        <v>0.81335269063799</v>
       </c>
       <c r="Q35" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="R35" t="n">
-        <v>12.55</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>59000</v>
+        <v>47200</v>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9429614653545474</v>
+        <v>0.92984721216669</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9489456895314872</v>
+        <v>0.943696710943188</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9416996441111212</v>
+        <v>0.9340556989457064</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9969264249657016</v>
+        <v>0.99485287839326</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9804345866924186</v>
+        <v>0.9767116685991836</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7625791836650271</v>
+        <v>0.7397020484446482</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8727505851385924</v>
+        <v>0.8691888880805203</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8419347693006257</v>
+        <v>0.8359693845540228</v>
       </c>
       <c r="L36" t="n">
-        <v>0.940491720410766</v>
+        <v>0.9374335582126658</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6636780197727512</v>
+        <v>0.6620310579283838</v>
       </c>
       <c r="N36" t="n">
-        <v>0.8057701366735179</v>
+        <v>0.8044424004118219</v>
       </c>
       <c r="O36" t="n">
-        <v>0.7431783334911648</v>
+        <v>0.7391068456697933</v>
       </c>
       <c r="P36" t="n">
-        <v>0.8148973415987896</v>
+        <v>0.8146765167844232</v>
       </c>
       <c r="Q36" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="R36" t="n">
-        <v>13.8</v>
+        <v>10.81666666666667</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n">
-        <v>70800</v>
+        <v>47200</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>0.947975015039395</v>
+        <v>0.9146724907948376</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9547256518079512</v>
+        <v>0.9419665936197096</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9481156752157752</v>
+        <v>0.93363427281136</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9969552069380424</v>
+        <v>0.9944012291697076</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9823911078941158</v>
+        <v>0.9726987735213668</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7375458672243128</v>
+        <v>0.6933435229687333</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8724907712624634</v>
+        <v>0.8691289914849443</v>
       </c>
       <c r="K37" t="n">
-        <v>0.8383589585800946</v>
+        <v>0.8298058678045905</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9398660885626924</v>
+        <v>0.9359241211227798</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6593535392075937</v>
+        <v>0.6499828171443977</v>
       </c>
       <c r="N37" t="n">
-        <v>0.8072985215495005</v>
+        <v>0.800263232135082</v>
       </c>
       <c r="O37" t="n">
-        <v>0.7404184759180183</v>
+        <v>0.7303459012158257</v>
       </c>
       <c r="P37" t="n">
-        <v>0.8169906057701786</v>
+        <v>0.8117328105371352</v>
       </c>
       <c r="Q37" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="R37" t="n">
-        <v>12.55</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n">
-        <v>70800</v>
+        <v>47200</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9380591604786832</v>
+        <v>0.918064163802092</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9477383695168616</v>
+        <v>0.938211042219024</v>
       </c>
       <c r="F38" t="n">
-        <v>0.939519043225038</v>
+        <v>0.9287821071349718</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9966535684819676</v>
+        <v>0.9929896251742144</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9808685603497546</v>
+        <v>0.9688414449043776</v>
       </c>
       <c r="I38" t="n">
-        <v>0.742353546879274</v>
+        <v>0.7700384226033601</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8740768852197996</v>
+        <v>0.8707536622429328</v>
       </c>
       <c r="K38" t="n">
-        <v>0.8421510773488949</v>
+        <v>0.8368102252754157</v>
       </c>
       <c r="L38" t="n">
-        <v>0.9417038181101494</v>
+        <v>0.9399456963197156</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6577075341630716</v>
+        <v>0.6564528852310708</v>
       </c>
       <c r="N38" t="n">
-        <v>0.8069683143066642</v>
+        <v>0.8043689068083948</v>
       </c>
       <c r="O38" t="n">
-        <v>0.7423884260584679</v>
+        <v>0.7377460960026445</v>
       </c>
       <c r="P38" t="n">
-        <v>0.8168263696113924</v>
+        <v>0.8149876056429437</v>
       </c>
       <c r="Q38" t="n">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="R38" t="n">
-        <v>15.18333333333333</v>
+        <v>15.11666666666667</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>70800</v>
+        <v>47200</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9392166748826286</v>
+        <v>0.9313907249921848</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9533960932930948</v>
+        <v>0.949651177898118</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9464959514522112</v>
+        <v>0.9421962819217192</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9971899842449428</v>
+        <v>0.9960872522677164</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9832111130615792</v>
+        <v>0.9807437378988296</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7403455689596031</v>
+        <v>0.7322804175806479</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8737186671349323</v>
+        <v>0.8729110706613373</v>
       </c>
       <c r="K39" t="n">
-        <v>0.8417926823417987</v>
+        <v>0.8397079945820725</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9413490105925548</v>
+        <v>0.939884957116312</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6610431269873112</v>
+        <v>0.6604173321696498</v>
       </c>
       <c r="N39" t="n">
-        <v>0.8071573549873249</v>
+        <v>0.8078586174694039</v>
       </c>
       <c r="O39" t="n">
-        <v>0.7425878579852564</v>
+        <v>0.7408824816114105</v>
       </c>
       <c r="P39" t="n">
-        <v>0.8173713192077531</v>
+        <v>0.8187539710359208</v>
       </c>
       <c r="Q39" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="R39" t="n">
-        <v>13.83333333333333</v>
+        <v>12.81666666666667</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B40" t="n">
-        <v>70800</v>
+        <v>47200</v>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9395204861522028</v>
+        <v>0.9296976424063218</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9570685381541376</v>
+        <v>0.9453215659706676</v>
       </c>
       <c r="F40" t="n">
-        <v>0.950595112134328</v>
+        <v>0.9370059701139504</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9966077185620476</v>
+        <v>0.9958277215542408</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9828963198544868</v>
+        <v>0.9787427087987824</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7711876032373161</v>
+        <v>0.7453034863088969</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8731166685790606</v>
+        <v>0.8723629042456653</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8410052027944792</v>
+        <v>0.8374289445531853</v>
       </c>
       <c r="L40" t="n">
-        <v>0.940863832397249</v>
+        <v>0.9391722933832856</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6588595688902609</v>
+        <v>0.655669719506964</v>
       </c>
       <c r="N40" t="n">
-        <v>0.8075003449596443</v>
+        <v>0.8060707683491749</v>
       </c>
       <c r="O40" t="n">
-        <v>0.7395595174351168</v>
+        <v>0.7397038260594128</v>
       </c>
       <c r="P40" t="n">
-        <v>0.8172853171377856</v>
+        <v>0.8163032801756489</v>
       </c>
       <c r="Q40" t="n">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="R40" t="n">
-        <v>14.16666666666667</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>70800</v>
+        <v>47200</v>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D41" t="n">
-        <v>0.944127196810968</v>
+        <v>0.927115523325721</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9514388855946934</v>
+        <v>0.9492648792597164</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9442076077029558</v>
+        <v>0.941882253221654</v>
       </c>
       <c r="G41" t="n">
-        <v>0.996487940165558</v>
+        <v>0.9957329559801776</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9808808730023876</v>
+        <v>0.9796383661906304</v>
       </c>
       <c r="I41" t="n">
-        <v>0.756934489829637</v>
+        <v>0.7427054376823459</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8729789870133738</v>
+        <v>0.8728151745695976</v>
       </c>
       <c r="K41" t="n">
-        <v>0.8420415698928418</v>
+        <v>0.842034594591218</v>
       </c>
       <c r="L41" t="n">
-        <v>0.9411759339992808</v>
+        <v>0.939895749499262</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6598727261140009</v>
+        <v>0.6618191350867594</v>
       </c>
       <c r="N41" t="n">
-        <v>0.8082038768997647</v>
+        <v>0.8070522019556594</v>
       </c>
       <c r="O41" t="n">
-        <v>0.7429406495214328</v>
+        <v>0.7420357941845869</v>
       </c>
       <c r="P41" t="n">
-        <v>0.8183230383286006</v>
+        <v>0.817108258256831</v>
       </c>
       <c r="Q41" t="n">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="R41" t="n">
-        <v>14.26666666666667</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B42" t="n">
-        <v>70800</v>
+        <v>59000</v>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9414472267692582</v>
+        <v>0.9450822917216352</v>
       </c>
       <c r="E42" t="n">
-        <v>0.954869278307002</v>
+        <v>0.95368729916892</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9480926249771072</v>
+        <v>0.9467688761017076</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9971840343200296</v>
+        <v>0.997248350724816</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9835213811511556</v>
+        <v>0.9837458558488216</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7443415702987111</v>
+        <v>0.7435869768649381</v>
       </c>
       <c r="J42" t="n">
-        <v>0.874968320544125</v>
+        <v>0.8732929104895372</v>
       </c>
       <c r="K42" t="n">
-        <v>0.8425395322466869</v>
+        <v>0.8425941190681121</v>
       </c>
       <c r="L42" t="n">
-        <v>0.9426497167054824</v>
+        <v>0.9402653682834532</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6610014997502058</v>
+        <v>0.6621792561332547</v>
       </c>
       <c r="N42" t="n">
-        <v>0.8080845098222513</v>
+        <v>0.8089306554120294</v>
       </c>
       <c r="O42" t="n">
-        <v>0.7428101691950146</v>
+        <v>0.7419770018386795</v>
       </c>
       <c r="P42" t="n">
-        <v>0.8186442689754233</v>
+        <v>0.8193517568898759</v>
       </c>
       <c r="Q42" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="R42" t="n">
-        <v>15.05</v>
+        <v>12.56666666666667</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B43" t="n">
-        <v>70800</v>
+        <v>59000</v>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>0.941886251325024</v>
+        <v>0.9464379106329192</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9545173942375996</v>
+        <v>0.9544645044911946</v>
       </c>
       <c r="F43" t="n">
-        <v>0.947619485637886</v>
+        <v>0.9474560794252062</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9969109330115916</v>
+        <v>0.9970289528641032</v>
       </c>
       <c r="H43" t="n">
-        <v>0.98338006401097</v>
+        <v>0.9837056952216936</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7582000324429862</v>
+        <v>0.7492749628440949</v>
       </c>
       <c r="J43" t="n">
-        <v>0.8727884745797796</v>
+        <v>0.8732689411170007</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8430424046092511</v>
+        <v>0.8416839789049813</v>
       </c>
       <c r="L43" t="n">
-        <v>0.940934438781112</v>
+        <v>0.9409356097867206</v>
       </c>
       <c r="M43" t="n">
-        <v>0.6632134546001011</v>
+        <v>0.6627889652452797</v>
       </c>
       <c r="N43" t="n">
-        <v>0.8083690198037974</v>
+        <v>0.8085982981000351</v>
       </c>
       <c r="O43" t="n">
-        <v>0.7435576891217452</v>
+        <v>0.7409673787705788</v>
       </c>
       <c r="P43" t="n">
-        <v>0.8179563640072168</v>
+        <v>0.8185309543026117</v>
       </c>
       <c r="Q43" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="R43" t="n">
-        <v>13.78333333333333</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B44" t="n">
-        <v>82600</v>
+        <v>59000</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9457441906969616</v>
+        <v>0.9403759368069043</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9551416794131004</v>
+        <v>0.9527885741541928</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9482926296791924</v>
+        <v>0.9457766502822804</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9970126736971912</v>
+        <v>0.9969758619942594</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9830460680613931</v>
+        <v>0.9820748569553458</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7455896475768952</v>
+        <v>0.764655906773352</v>
       </c>
       <c r="J44" t="n">
-        <v>0.8749778376476799</v>
+        <v>0.8727684165419266</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8410136550233889</v>
+        <v>0.8385335095291163</v>
       </c>
       <c r="L44" t="n">
-        <v>0.9414790777497608</v>
+        <v>0.939575232620489</v>
       </c>
       <c r="M44" t="n">
-        <v>0.6556508149673319</v>
+        <v>0.6587903043554871</v>
       </c>
       <c r="N44" t="n">
-        <v>0.8061986700393822</v>
+        <v>0.8078466773089217</v>
       </c>
       <c r="O44" t="n">
-        <v>0.7395911058434977</v>
+        <v>0.7389152677047097</v>
       </c>
       <c r="P44" t="n">
-        <v>0.8172174943648643</v>
+        <v>0.8185382604496779</v>
       </c>
       <c r="Q44" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="R44" t="n">
-        <v>14.06666666666667</v>
+        <v>12.78333333333333</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B45" t="n">
-        <v>82600</v>
+        <v>59000</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9448155386886647</v>
+        <v>0.9229081615243822</v>
       </c>
       <c r="E45" t="n">
-        <v>0.956942602942589</v>
+        <v>0.9380432618316792</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9507855714289308</v>
+        <v>0.9287531447120227</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9969989030817292</v>
+        <v>0.9942760696357538</v>
       </c>
       <c r="H45" t="n">
-        <v>0.98375742746622</v>
+        <v>0.9726019344435572</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7749983647451933</v>
+        <v>0.743154407698794</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8750106016685475</v>
+        <v>0.8710102913893063</v>
       </c>
       <c r="K45" t="n">
-        <v>0.8428706559100203</v>
+        <v>0.8344784355225043</v>
       </c>
       <c r="L45" t="n">
-        <v>0.9420328240906812</v>
+        <v>0.9383955837050448</v>
       </c>
       <c r="M45" t="n">
-        <v>0.6587364348852974</v>
+        <v>0.6475929231450921</v>
       </c>
       <c r="N45" t="n">
-        <v>0.8111715029922874</v>
+        <v>0.8065769274099287</v>
       </c>
       <c r="O45" t="n">
-        <v>0.7401408492049697</v>
+        <v>0.7305660495634267</v>
       </c>
       <c r="P45" t="n">
-        <v>0.8221226132269213</v>
+        <v>0.8186355022673789</v>
       </c>
       <c r="Q45" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="R45" t="n">
-        <v>14.81666666666667</v>
+        <v>12.71666666666667</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B46" t="n">
-        <v>82600</v>
+        <v>59000</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9485027518748111</v>
+        <v>0.9422263516710035</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9569233446400508</v>
+        <v>0.9524726690468264</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9508535021074253</v>
+        <v>0.945176136529832</v>
       </c>
       <c r="G46" t="n">
-        <v>0.997691284163018</v>
+        <v>0.9969995605030968</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9865033047520788</v>
+        <v>0.9819711777839424</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7200444792459235</v>
+        <v>0.7330641098624189</v>
       </c>
       <c r="J46" t="n">
-        <v>0.8724448071705336</v>
+        <v>0.8703361892777384</v>
       </c>
       <c r="K46" t="n">
-        <v>0.838977325397926</v>
+        <v>0.8350299161376199</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9394449578706908</v>
+        <v>0.9380088743711472</v>
       </c>
       <c r="M46" t="n">
-        <v>0.6523020410221908</v>
+        <v>0.662235000811101</v>
       </c>
       <c r="N46" t="n">
-        <v>0.8082651848519049</v>
+        <v>0.8045592516403307</v>
       </c>
       <c r="O46" t="n">
-        <v>0.7361769366253152</v>
+        <v>0.7377961446805361</v>
       </c>
       <c r="P46" t="n">
-        <v>0.819568046156175</v>
+        <v>0.8149206140169738</v>
       </c>
       <c r="Q46" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="R46" t="n">
-        <v>14.33333333333333</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>82600</v>
+        <v>59000</v>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>0.939185341663074</v>
+        <v>0.936110770714384</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9514099178757508</v>
+        <v>0.9557945174434226</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9437863874318499</v>
+        <v>0.9495095839149756</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9975370548468389</v>
+        <v>0.9972637800168904</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9847582447826736</v>
+        <v>0.9832267630709924</v>
       </c>
       <c r="I47" t="n">
-        <v>0.736385581055404</v>
+        <v>0.7669494621256233</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8736934280608399</v>
+        <v>0.8732016939501598</v>
       </c>
       <c r="K47" t="n">
-        <v>0.8391833019393402</v>
+        <v>0.8401755912550641</v>
       </c>
       <c r="L47" t="n">
-        <v>0.940601957649406</v>
+        <v>0.9403720773026432</v>
       </c>
       <c r="M47" t="n">
-        <v>0.6566627588625303</v>
+        <v>0.6618220041719367</v>
       </c>
       <c r="N47" t="n">
-        <v>0.8088901024596624</v>
+        <v>0.8068657634093013</v>
       </c>
       <c r="O47" t="n">
-        <v>0.7403540707441751</v>
+        <v>0.7411638982703711</v>
       </c>
       <c r="P47" t="n">
-        <v>0.82008857103447</v>
+        <v>0.8171452938949734</v>
       </c>
       <c r="Q47" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="R47" t="n">
-        <v>14.55</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n">
-        <v>82600</v>
+        <v>59000</v>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D48" t="n">
-        <v>0.94154395226141</v>
+        <v>0.9429614653545474</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9504164436879016</v>
+        <v>0.9489456895314872</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9429710836368908</v>
+        <v>0.9416996441111212</v>
       </c>
       <c r="G48" t="n">
-        <v>0.995942962456372</v>
+        <v>0.9969264249657016</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9791469044699244</v>
+        <v>0.9804345866924186</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7510831163705745</v>
+        <v>0.7625791836650271</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8728375754113245</v>
+        <v>0.8727505851385924</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8390430251764351</v>
+        <v>0.8419347693006257</v>
       </c>
       <c r="L48" t="n">
-        <v>0.9401722427346262</v>
+        <v>0.940491720410766</v>
       </c>
       <c r="M48" t="n">
-        <v>0.6554710916227673</v>
+        <v>0.6636780197727512</v>
       </c>
       <c r="N48" t="n">
-        <v>0.805291805501725</v>
+        <v>0.8057701366735179</v>
       </c>
       <c r="O48" t="n">
-        <v>0.7370598035224933</v>
+        <v>0.7431783334911648</v>
       </c>
       <c r="P48" t="n">
-        <v>0.8157609442933567</v>
+        <v>0.8148973415987896</v>
       </c>
       <c r="Q48" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="R48" t="n">
-        <v>14.46666666666667</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>82600</v>
+        <v>59000</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9418888592517266</v>
+        <v>0.940382850974272</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9540625182126072</v>
+        <v>0.9514061680637528</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9471814721621112</v>
+        <v>0.94407383801241</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9973150780173542</v>
+        <v>0.9968941451565008</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9842630890198522</v>
+        <v>0.9818976847197046</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7401348451020151</v>
+        <v>0.7182099777146236</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8711581596318627</v>
+        <v>0.8726806699641901</v>
       </c>
       <c r="K49" t="n">
-        <v>0.8359828386973279</v>
+        <v>0.8382047628100107</v>
       </c>
       <c r="L49" t="n">
-        <v>0.9376734453081734</v>
+        <v>0.9387147804977608</v>
       </c>
       <c r="M49" t="n">
-        <v>0.6543953594183962</v>
+        <v>0.6555586242118278</v>
       </c>
       <c r="N49" t="n">
-        <v>0.8084957747901144</v>
+        <v>0.804206070381053</v>
       </c>
       <c r="O49" t="n">
-        <v>0.7365209551548627</v>
+        <v>0.7381531921095241</v>
       </c>
       <c r="P49" t="n">
-        <v>0.81932946593435</v>
+        <v>0.8139683212054213</v>
       </c>
       <c r="Q49" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="R49" t="n">
-        <v>11.88333333333333</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B50" t="n">
-        <v>82600</v>
+        <v>59000</v>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9438955217940328</v>
+        <v>0.9301207697348444</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9503226070002952</v>
+        <v>0.9500854714235684</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9428721518633556</v>
+        <v>0.942731817914369</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9967617913637375</v>
+        <v>0.996892527051164</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9822326454596684</v>
+        <v>0.981971579998649</v>
       </c>
       <c r="I50" t="n">
-        <v>0.7209814771778669</v>
+        <v>0.7457901670941616</v>
       </c>
       <c r="J50" t="n">
-        <v>0.8745239899277127</v>
+        <v>0.8720579755326359</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8386843087939903</v>
+        <v>0.8385422647448013</v>
       </c>
       <c r="L50" t="n">
-        <v>0.9406314416056036</v>
+        <v>0.9393235277572316</v>
       </c>
       <c r="M50" t="n">
-        <v>0.654720944407204</v>
+        <v>0.6616977930359352</v>
       </c>
       <c r="N50" t="n">
-        <v>0.8059392928398293</v>
+        <v>0.8079701147175844</v>
       </c>
       <c r="O50" t="n">
-        <v>0.740031874222058</v>
+        <v>0.7407472178391501</v>
       </c>
       <c r="P50" t="n">
-        <v>0.8175919928336219</v>
+        <v>0.8181984866919181</v>
       </c>
       <c r="Q50" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="R50" t="n">
-        <v>15.78333333333333</v>
+        <v>15.23333333333333</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>94400</v>
+        <v>59000</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9546663770384696</v>
+        <v>0.935219367169673</v>
       </c>
       <c r="E51" t="n">
-        <v>0.957081326397338</v>
+        <v>0.952894487563493</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9502168207416494</v>
+        <v>0.9458896085994632</v>
       </c>
       <c r="G51" t="n">
-        <v>0.997577313531962</v>
+        <v>0.9963966257925938</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9866359381095612</v>
+        <v>0.98068510631623</v>
       </c>
       <c r="I51" t="n">
-        <v>0.7556946090228501</v>
+        <v>0.7493969514828046</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8719982149943296</v>
+        <v>0.8747362979207984</v>
       </c>
       <c r="K51" t="n">
-        <v>0.8374462382142496</v>
+        <v>0.8426950525520615</v>
       </c>
       <c r="L51" t="n">
-        <v>0.9396507339510676</v>
+        <v>0.9418828367310365</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6602263995615884</v>
+        <v>0.6600887204498415</v>
       </c>
       <c r="N51" t="n">
-        <v>0.8059202698421778</v>
+        <v>0.8088112236608177</v>
       </c>
       <c r="O51" t="n">
-        <v>0.7407445548111533</v>
+        <v>0.7410457661988034</v>
       </c>
       <c r="P51" t="n">
-        <v>0.8153886089175844</v>
+        <v>0.8186194810445673</v>
       </c>
       <c r="Q51" t="n">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="R51" t="n">
-        <v>14.48333333333333</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B52" t="n">
-        <v>94400</v>
+        <v>70800</v>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9424942755042788</v>
+        <v>0.947975015039395</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9513886797624066</v>
+        <v>0.9547256518079512</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9436952433181786</v>
+        <v>0.9481156752157752</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9972522236109028</v>
+        <v>0.9969552069380424</v>
       </c>
       <c r="H52" t="n">
-        <v>0.984645820445304</v>
+        <v>0.9823911078941158</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7694087239010302</v>
+        <v>0.7375458672243128</v>
       </c>
       <c r="J52" t="n">
-        <v>0.8735426415534479</v>
+        <v>0.8724907712624634</v>
       </c>
       <c r="K52" t="n">
-        <v>0.8427287567496093</v>
+        <v>0.8383589585800946</v>
       </c>
       <c r="L52" t="n">
-        <v>0.9414094534933368</v>
+        <v>0.9398660885626924</v>
       </c>
       <c r="M52" t="n">
-        <v>0.6618580837175024</v>
+        <v>0.6593535392075937</v>
       </c>
       <c r="N52" t="n">
-        <v>0.8082797621732033</v>
+        <v>0.8072985215495005</v>
       </c>
       <c r="O52" t="n">
-        <v>0.7435750779575693</v>
+        <v>0.7404184759180183</v>
       </c>
       <c r="P52" t="n">
-        <v>0.8178795524953089</v>
+        <v>0.8169906057701786</v>
       </c>
       <c r="Q52" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R52" t="n">
-        <v>18.36666666666667</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
+        <v>60</v>
+      </c>
+      <c r="B53" t="n">
+        <v>70800</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.9380591604786832</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9477383695168616</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.939519043225038</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.9966535684819676</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.9808685603497546</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.742353546879274</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.8740768852197996</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.8421510773488949</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.9417038181101494</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.6577075341630716</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.8069683143066642</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.7423884260584679</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.8168263696113924</v>
+      </c>
+      <c r="Q53" t="n">
         <v>80</v>
       </c>
-      <c r="B53" t="n">
-        <v>94400</v>
-      </c>
-      <c r="C53" t="n">
-        <v>3</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.9411194273923644</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.9594305885386551</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.9538108076946986</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0.997114703040744</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.9832307634406978</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.7716912045780399</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0.8700569883724342</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0.8380297406039905</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0.9391556719398968</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0.658409251457021</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0.80797639733701</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0.7391992522467585</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0.8185612100085248</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>56</v>
-      </c>
       <c r="R53" t="n">
-        <v>15.31666666666667</v>
+        <v>15.18333333333333</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B54" t="n">
-        <v>94400</v>
+        <v>70800</v>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>0.9489018603627204</v>
+        <v>0.9392166748826286</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9535104267903139</v>
+        <v>0.9533960932930948</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9460612809842972</v>
+        <v>0.9464959514522112</v>
       </c>
       <c r="G54" t="n">
-        <v>0.9972724560657312</v>
+        <v>0.9971899842449428</v>
       </c>
       <c r="H54" t="n">
-        <v>0.9847909352872276</v>
+        <v>0.9832111130615792</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7581673316858651</v>
+        <v>0.7403455689596031</v>
       </c>
       <c r="J54" t="n">
-        <v>0.8738146454082072</v>
+        <v>0.8737186671349323</v>
       </c>
       <c r="K54" t="n">
-        <v>0.8392804035492261</v>
+        <v>0.8417926823417987</v>
       </c>
       <c r="L54" t="n">
-        <v>0.9407270986600602</v>
+        <v>0.9413490105925548</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6570876718101218</v>
+        <v>0.6610431269873112</v>
       </c>
       <c r="N54" t="n">
-        <v>0.8071220145696771</v>
+        <v>0.8071573549873249</v>
       </c>
       <c r="O54" t="n">
-        <v>0.7399602072278462</v>
+        <v>0.7425878579852564</v>
       </c>
       <c r="P54" t="n">
-        <v>0.8177748628761639</v>
+        <v>0.8173713192077531</v>
       </c>
       <c r="Q54" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="R54" t="n">
-        <v>16.71666666666667</v>
+        <v>13.83333333333333</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B55" t="n">
-        <v>94400</v>
+        <v>70800</v>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>0.9397218752300536</v>
+        <v>0.9395204861522028</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9518526342978376</v>
+        <v>0.9570685381541376</v>
       </c>
       <c r="F55" t="n">
-        <v>0.944560686862571</v>
+        <v>0.950595112134328</v>
       </c>
       <c r="G55" t="n">
-        <v>0.9965763544454054</v>
+        <v>0.9966077185620476</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9823168624012492</v>
+        <v>0.9828963198544868</v>
       </c>
       <c r="I55" t="n">
-        <v>0.7562151573040093</v>
+        <v>0.7711876032373161</v>
       </c>
       <c r="J55" t="n">
-        <v>0.8709856239952416</v>
+        <v>0.8731166685790606</v>
       </c>
       <c r="K55" t="n">
-        <v>0.8348739119505788</v>
+        <v>0.8410052027944792</v>
       </c>
       <c r="L55" t="n">
-        <v>0.938654981675015</v>
+        <v>0.940863832397249</v>
       </c>
       <c r="M55" t="n">
-        <v>0.6516676424737817</v>
+        <v>0.6588595688902609</v>
       </c>
       <c r="N55" t="n">
-        <v>0.8039748422807005</v>
+        <v>0.8075003449596443</v>
       </c>
       <c r="O55" t="n">
-        <v>0.7348208840343594</v>
+        <v>0.7395595174351168</v>
       </c>
       <c r="P55" t="n">
-        <v>0.814729936654675</v>
+        <v>0.8172853171377856</v>
       </c>
       <c r="Q55" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="R55" t="n">
-        <v>14.18333333333333</v>
+        <v>14.16666666666667</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B56" t="n">
-        <v>94400</v>
+        <v>70800</v>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>0.9356291983233532</v>
+        <v>0.944127196810968</v>
       </c>
       <c r="E56" t="n">
-        <v>0.954337943763608</v>
+        <v>0.9514388855946934</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9477702211057863</v>
+        <v>0.9442076077029558</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9965328705234529</v>
+        <v>0.996487940165558</v>
       </c>
       <c r="H56" t="n">
-        <v>0.9817913734124299</v>
+        <v>0.9808808730023876</v>
       </c>
       <c r="I56" t="n">
-        <v>0.771309286923576</v>
+        <v>0.756934489829637</v>
       </c>
       <c r="J56" t="n">
-        <v>0.8731585360783415</v>
+        <v>0.8729789870133738</v>
       </c>
       <c r="K56" t="n">
-        <v>0.8405455371960827</v>
+        <v>0.8420415698928418</v>
       </c>
       <c r="L56" t="n">
-        <v>0.94020599328905</v>
+        <v>0.9411759339992808</v>
       </c>
       <c r="M56" t="n">
-        <v>0.6542075308042019</v>
+        <v>0.6598727261140009</v>
       </c>
       <c r="N56" t="n">
-        <v>0.8078887191119754</v>
+        <v>0.8082038768997647</v>
       </c>
       <c r="O56" t="n">
-        <v>0.7399658212273187</v>
+        <v>0.7429406495214328</v>
       </c>
       <c r="P56" t="n">
-        <v>0.8177748683312027</v>
+        <v>0.8183230383286006</v>
       </c>
       <c r="Q56" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R56" t="n">
-        <v>17.95</v>
+        <v>14.26666666666667</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n">
-        <v>94400</v>
+        <v>70800</v>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>0.9484169512384232</v>
+        <v>0.9414472267692582</v>
       </c>
       <c r="E57" t="n">
-        <v>0.956628840607007</v>
+        <v>0.954869278307002</v>
       </c>
       <c r="F57" t="n">
-        <v>0.94999664904235</v>
+        <v>0.9480926249771072</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9977331003940448</v>
+        <v>0.9971840343200296</v>
       </c>
       <c r="H57" t="n">
-        <v>0.9858424598267368</v>
+        <v>0.9835213811511556</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7557035376395974</v>
+        <v>0.7443415702987111</v>
       </c>
       <c r="J57" t="n">
-        <v>0.872120859472996</v>
+        <v>0.874968320544125</v>
       </c>
       <c r="K57" t="n">
-        <v>0.8396817491828032</v>
+        <v>0.8425395322466869</v>
       </c>
       <c r="L57" t="n">
-        <v>0.9397557743255218</v>
+        <v>0.9426497167054824</v>
       </c>
       <c r="M57" t="n">
-        <v>0.6596945170230167</v>
+        <v>0.6610014997502058</v>
       </c>
       <c r="N57" t="n">
-        <v>0.809061510331918</v>
+        <v>0.8080845098222513</v>
       </c>
       <c r="O57" t="n">
-        <v>0.7406338670040999</v>
+        <v>0.7428101691950146</v>
       </c>
       <c r="P57" t="n">
-        <v>0.8202131116491798</v>
+        <v>0.8186442689754233</v>
       </c>
       <c r="Q57" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="R57" t="n">
-        <v>15.1</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n">
-        <v>106200</v>
+        <v>70800</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9531955185514076</v>
+        <v>0.941886251325024</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9636854727512968</v>
+        <v>0.9545173942375996</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9584891458362936</v>
+        <v>0.947619485637886</v>
       </c>
       <c r="G58" t="n">
-        <v>0.997493608820884</v>
+        <v>0.9969109330115916</v>
       </c>
       <c r="H58" t="n">
-        <v>0.986279955434324</v>
+        <v>0.98338006401097</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7683151533411842</v>
+        <v>0.7582000324429862</v>
       </c>
       <c r="J58" t="n">
-        <v>0.8762759692884033</v>
+        <v>0.8727884745797796</v>
       </c>
       <c r="K58" t="n">
-        <v>0.8423613271854093</v>
+        <v>0.8430424046092511</v>
       </c>
       <c r="L58" t="n">
-        <v>0.9421739288535952</v>
+        <v>0.940934438781112</v>
       </c>
       <c r="M58" t="n">
-        <v>0.6583535421750554</v>
+        <v>0.6632134546001011</v>
       </c>
       <c r="N58" t="n">
-        <v>0.8083586802871759</v>
+        <v>0.8083690198037974</v>
       </c>
       <c r="O58" t="n">
-        <v>0.743621110989294</v>
+        <v>0.7435576891217452</v>
       </c>
       <c r="P58" t="n">
-        <v>0.8186903687218439</v>
+        <v>0.8179563640072168</v>
       </c>
       <c r="Q58" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="R58" t="n">
-        <v>16.06666666666667</v>
+        <v>13.78333333333333</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="B59" t="n">
-        <v>106200</v>
+        <v>70800</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9469192111086738</v>
+        <v>0.9364774427083112</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9551608546973572</v>
+        <v>0.9540903754086636</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9485476208807176</v>
+        <v>0.9475186710586015</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9974129275844704</v>
+        <v>0.9963312397898864</v>
       </c>
       <c r="H59" t="n">
-        <v>0.9845698917626264</v>
+        <v>0.9799025593870152</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7687400943204908</v>
+        <v>0.7475745647139094</v>
       </c>
       <c r="J59" t="n">
-        <v>0.8689972744944023</v>
+        <v>0.8742952325196779</v>
       </c>
       <c r="K59" t="n">
-        <v>0.8361838103755503</v>
+        <v>0.8388437734780536</v>
       </c>
       <c r="L59" t="n">
-        <v>0.9376646658645432</v>
+        <v>0.9407959303326616</v>
       </c>
       <c r="M59" t="n">
-        <v>0.6588145708512607</v>
+        <v>0.652841178522658</v>
       </c>
       <c r="N59" t="n">
-        <v>0.8050105893759524</v>
+        <v>0.8069097208832418</v>
       </c>
       <c r="O59" t="n">
-        <v>0.7381659056277133</v>
+        <v>0.7379670542671287</v>
       </c>
       <c r="P59" t="n">
-        <v>0.8155866566130014</v>
+        <v>0.817642330059365</v>
       </c>
       <c r="Q59" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="R59" t="n">
-        <v>14.9</v>
+        <v>19.71666666666667</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="B60" t="n">
-        <v>106200</v>
+        <v>70800</v>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9579818232250884</v>
+        <v>0.9422310790953576</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9632865992480208</v>
+        <v>0.9511159578251668</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9578208735507217</v>
+        <v>0.9437806704895682</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9979155358095236</v>
+        <v>0.9969163589297438</v>
       </c>
       <c r="H60" t="n">
-        <v>0.9876369860899288</v>
+        <v>0.9823686039453438</v>
       </c>
       <c r="I60" t="n">
-        <v>0.7615340800258081</v>
+        <v>0.7647576576434653</v>
       </c>
       <c r="J60" t="n">
-        <v>0.8751961488924892</v>
+        <v>0.872165959861</v>
       </c>
       <c r="K60" t="n">
-        <v>0.8430651501132558</v>
+        <v>0.8397038284683904</v>
       </c>
       <c r="L60" t="n">
-        <v>0.9420133834052647</v>
+        <v>0.940455292777586</v>
       </c>
       <c r="M60" t="n">
-        <v>0.6613323351674056</v>
+        <v>0.6600485669500699</v>
       </c>
       <c r="N60" t="n">
-        <v>0.8098157079701707</v>
+        <v>0.8081895461039789</v>
       </c>
       <c r="O60" t="n">
-        <v>0.7427121718312089</v>
+        <v>0.741531216096151</v>
       </c>
       <c r="P60" t="n">
-        <v>0.8206530630887496</v>
+        <v>0.8187860807053366</v>
       </c>
       <c r="Q60" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="R60" t="n">
-        <v>17.46666666666667</v>
+        <v>14.71666666666667</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>106200</v>
+        <v>70800</v>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D61" t="n">
-        <v>0.9532049569333728</v>
+        <v>0.9486679035021358</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9546766025091176</v>
+        <v>0.9552757801079858</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9476246479199996</v>
+        <v>0.9486802460641266</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9966132182113084</v>
+        <v>0.997162781281468</v>
       </c>
       <c r="H61" t="n">
-        <v>0.984501495801418</v>
+        <v>0.9843408345659532</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7735815244546442</v>
+        <v>0.7308928771090828</v>
       </c>
       <c r="J61" t="n">
-        <v>0.8745941072542824</v>
+        <v>0.87425627174676</v>
       </c>
       <c r="K61" t="n">
-        <v>0.8431710167500561</v>
+        <v>0.8393971046942257</v>
       </c>
       <c r="L61" t="n">
-        <v>0.9423114762528432</v>
+        <v>0.941332147054694</v>
       </c>
       <c r="M61" t="n">
-        <v>0.6616089577629435</v>
+        <v>0.6566208361600481</v>
       </c>
       <c r="N61" t="n">
-        <v>0.8104829243657274</v>
+        <v>0.8063979772812079</v>
       </c>
       <c r="O61" t="n">
-        <v>0.7435834878506159</v>
+        <v>0.7390717529421374</v>
       </c>
       <c r="P61" t="n">
-        <v>0.8210178308723513</v>
+        <v>0.8177549397606371</v>
       </c>
       <c r="Q61" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="R61" t="n">
-        <v>16.18333333333333</v>
+        <v>13.58333333333333</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B62" t="n">
-        <v>106200</v>
+        <v>82600</v>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>0.9504529135702084</v>
+        <v>0.9457441906969616</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9587232135099436</v>
+        <v>0.9551416794131004</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9527897409436</v>
+        <v>0.9482926296791924</v>
       </c>
       <c r="G62" t="n">
-        <v>0.997330969760432</v>
+        <v>0.9970126736971912</v>
       </c>
       <c r="H62" t="n">
-        <v>0.9848811854136562</v>
+        <v>0.9830460680613931</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7568449273785216</v>
+        <v>0.7455896475768952</v>
       </c>
       <c r="J62" t="n">
-        <v>0.8722448065903878</v>
+        <v>0.8749778376476799</v>
       </c>
       <c r="K62" t="n">
-        <v>0.8392564274533871</v>
+        <v>0.8410136550233889</v>
       </c>
       <c r="L62" t="n">
-        <v>0.9395916534218856</v>
+        <v>0.9414790777497608</v>
       </c>
       <c r="M62" t="n">
-        <v>0.6590101574601378</v>
+        <v>0.6556508149673319</v>
       </c>
       <c r="N62" t="n">
-        <v>0.8059289940531303</v>
+        <v>0.8061986700393822</v>
       </c>
       <c r="O62" t="n">
-        <v>0.7393247225205706</v>
+        <v>0.7395911058434977</v>
       </c>
       <c r="P62" t="n">
-        <v>0.8167159754420152</v>
+        <v>0.8172174943648643</v>
       </c>
       <c r="Q62" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="R62" t="n">
-        <v>14.6</v>
+        <v>14.06666666666667</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B63" t="n">
-        <v>106200</v>
+        <v>82600</v>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>0.952835755810804</v>
+        <v>0.9448155386886647</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9625114325988172</v>
+        <v>0.956942602942589</v>
       </c>
       <c r="F63" t="n">
-        <v>0.957129538124336</v>
+        <v>0.9507855714289308</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9973208972633356</v>
+        <v>0.9969989030817292</v>
       </c>
       <c r="H63" t="n">
-        <v>0.9857055843429776</v>
+        <v>0.98375742746622</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7531687696648588</v>
+        <v>0.7749983647451933</v>
       </c>
       <c r="J63" t="n">
-        <v>0.8733310739789409</v>
+        <v>0.8750106016685475</v>
       </c>
       <c r="K63" t="n">
-        <v>0.8413182433976796</v>
+        <v>0.8428706559100203</v>
       </c>
       <c r="L63" t="n">
-        <v>0.9405744351762666</v>
+        <v>0.9420328240906812</v>
       </c>
       <c r="M63" t="n">
-        <v>0.6624739464162389</v>
+        <v>0.6587364348852974</v>
       </c>
       <c r="N63" t="n">
-        <v>0.8070805943811136</v>
+        <v>0.8111715029922874</v>
       </c>
       <c r="O63" t="n">
-        <v>0.7418485188370584</v>
+        <v>0.7401408492049697</v>
       </c>
       <c r="P63" t="n">
-        <v>0.8170582477717524</v>
+        <v>0.8221226132269213</v>
       </c>
       <c r="Q63" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="R63" t="n">
         <v>14.81666666666667</v>
@@ -4631,338 +4631,2130 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="B64" t="n">
-        <v>118000</v>
+        <v>82600</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>0.9514708777834512</v>
+        <v>0.9485027518748111</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9541599806109756</v>
+        <v>0.9569233446400508</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9471844988519482</v>
+        <v>0.9508535021074253</v>
       </c>
       <c r="G64" t="n">
-        <v>0.9960358031375868</v>
+        <v>0.997691284163018</v>
       </c>
       <c r="H64" t="n">
-        <v>0.9810192240648744</v>
+        <v>0.9865033047520788</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7852531269396714</v>
+        <v>0.7200444792459235</v>
       </c>
       <c r="J64" t="n">
-        <v>0.870669907746362</v>
+        <v>0.8724448071705336</v>
       </c>
       <c r="K64" t="n">
-        <v>0.8383495495189892</v>
+        <v>0.838977325397926</v>
       </c>
       <c r="L64" t="n">
-        <v>0.9392158945854632</v>
+        <v>0.9394449578706908</v>
       </c>
       <c r="M64" t="n">
-        <v>0.6575203635321591</v>
+        <v>0.6523020410221908</v>
       </c>
       <c r="N64" t="n">
-        <v>0.8075862568927561</v>
+        <v>0.8082651848519049</v>
       </c>
       <c r="O64" t="n">
-        <v>0.7368017654412373</v>
+        <v>0.7361769366253152</v>
       </c>
       <c r="P64" t="n">
-        <v>0.8176647333656863</v>
+        <v>0.819568046156175</v>
       </c>
       <c r="Q64" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R64" t="n">
-        <v>18.11666666666667</v>
+        <v>14.33333333333333</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="B65" t="n">
-        <v>118000</v>
+        <v>82600</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>0.955915774255244</v>
+        <v>0.939185341663074</v>
       </c>
       <c r="E65" t="n">
-        <v>0.960477275902818</v>
+        <v>0.9514099178757508</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9548526902997456</v>
+        <v>0.9437863874318499</v>
       </c>
       <c r="G65" t="n">
-        <v>0.9974607783425116</v>
+        <v>0.9975370548468389</v>
       </c>
       <c r="H65" t="n">
-        <v>0.9858744696137952</v>
+        <v>0.9847582447826736</v>
       </c>
       <c r="I65" t="n">
-        <v>0.7390462201882121</v>
+        <v>0.736385581055404</v>
       </c>
       <c r="J65" t="n">
-        <v>0.8729358050742839</v>
+        <v>0.8736934280608399</v>
       </c>
       <c r="K65" t="n">
-        <v>0.8383687442576484</v>
+        <v>0.8391833019393402</v>
       </c>
       <c r="L65" t="n">
-        <v>0.9403738118222396</v>
+        <v>0.940601957649406</v>
       </c>
       <c r="M65" t="n">
-        <v>0.6588119869376617</v>
+        <v>0.6566627588625303</v>
       </c>
       <c r="N65" t="n">
-        <v>0.8071772707983176</v>
+        <v>0.8088901024596624</v>
       </c>
       <c r="O65" t="n">
-        <v>0.7401098810032755</v>
+        <v>0.7403540707441751</v>
       </c>
       <c r="P65" t="n">
-        <v>0.8173234305099706</v>
+        <v>0.82008857103447</v>
       </c>
       <c r="Q65" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="R65" t="n">
-        <v>14.23333333333333</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="B66" t="n">
-        <v>118000</v>
+        <v>82600</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>0.9472369725599482</v>
+        <v>0.94154395226141</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9597118205387848</v>
+        <v>0.9504164436879016</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9539495244885684</v>
+        <v>0.9429710836368908</v>
       </c>
       <c r="G66" t="n">
-        <v>0.9973276594821128</v>
+        <v>0.995942962456372</v>
       </c>
       <c r="H66" t="n">
-        <v>0.984744103304552</v>
+        <v>0.9791469044699244</v>
       </c>
       <c r="I66" t="n">
-        <v>0.7522940535459072</v>
+        <v>0.7510831163705745</v>
       </c>
       <c r="J66" t="n">
-        <v>0.8700817860425122</v>
+        <v>0.8728375754113245</v>
       </c>
       <c r="K66" t="n">
-        <v>0.8399263294110075</v>
+        <v>0.8390430251764351</v>
       </c>
       <c r="L66" t="n">
-        <v>0.939455283837618</v>
+        <v>0.9401722427346262</v>
       </c>
       <c r="M66" t="n">
-        <v>0.6606360166364864</v>
+        <v>0.6554710916227673</v>
       </c>
       <c r="N66" t="n">
-        <v>0.8066930050414558</v>
+        <v>0.805291805501725</v>
       </c>
       <c r="O66" t="n">
-        <v>0.7419078497438281</v>
+        <v>0.7370598035224933</v>
       </c>
       <c r="P66" t="n">
-        <v>0.8170707624376189</v>
+        <v>0.8157609442933567</v>
       </c>
       <c r="Q66" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="R66" t="n">
-        <v>17.1</v>
+        <v>14.46666666666667</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n">
-        <v>118000</v>
+        <v>82600</v>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D67" t="n">
-        <v>0.9412710564802362</v>
+        <v>0.9418888592517266</v>
       </c>
       <c r="E67" t="n">
-        <v>0.958476662416502</v>
+        <v>0.9540625182126072</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9522730459344352</v>
+        <v>0.9471814721621112</v>
       </c>
       <c r="G67" t="n">
-        <v>0.9974551300903688</v>
+        <v>0.9973150780173542</v>
       </c>
       <c r="H67" t="n">
-        <v>0.9861103244306182</v>
+        <v>0.9842630890198522</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7472653187845248</v>
+        <v>0.7401348451020151</v>
       </c>
       <c r="J67" t="n">
-        <v>0.8703936678523524</v>
+        <v>0.8711581596318627</v>
       </c>
       <c r="K67" t="n">
-        <v>0.8388422145938996</v>
+        <v>0.8359828386973279</v>
       </c>
       <c r="L67" t="n">
-        <v>0.9386725977844982</v>
+        <v>0.9376734453081734</v>
       </c>
       <c r="M67" t="n">
-        <v>0.6565330016788367</v>
+        <v>0.6543953594183962</v>
       </c>
       <c r="N67" t="n">
-        <v>0.8047120431249322</v>
+        <v>0.8084957747901144</v>
       </c>
       <c r="O67" t="n">
-        <v>0.7375722411552172</v>
+        <v>0.7365209551548627</v>
       </c>
       <c r="P67" t="n">
-        <v>0.8142219303808694</v>
+        <v>0.81932946593435</v>
       </c>
       <c r="Q67" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R67" t="n">
-        <v>17.4</v>
+        <v>11.88333333333333</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n">
-        <v>118000</v>
+        <v>82600</v>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D68" t="n">
-        <v>0.9514949544625052</v>
+        <v>0.9438955217940328</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9568749388752912</v>
+        <v>0.9503226070002952</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9501102797497194</v>
+        <v>0.9428721518633556</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9973468103816042</v>
+        <v>0.9967617913637375</v>
       </c>
       <c r="H68" t="n">
-        <v>0.985005291448583</v>
+        <v>0.9822326454596684</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7517535218631746</v>
+        <v>0.7209814771778669</v>
       </c>
       <c r="J68" t="n">
-        <v>0.8734997830242403</v>
+        <v>0.8745239899277127</v>
       </c>
       <c r="K68" t="n">
-        <v>0.8409518335786538</v>
+        <v>0.8386843087939903</v>
       </c>
       <c r="L68" t="n">
-        <v>0.9415155801244892</v>
+        <v>0.9406314416056036</v>
       </c>
       <c r="M68" t="n">
-        <v>0.6631342121523356</v>
+        <v>0.654720944407204</v>
       </c>
       <c r="N68" t="n">
-        <v>0.807864609367937</v>
+        <v>0.8059392928398293</v>
       </c>
       <c r="O68" t="n">
-        <v>0.743772850563051</v>
+        <v>0.740031874222058</v>
       </c>
       <c r="P68" t="n">
-        <v>0.8172368854986581</v>
+        <v>0.8175919928336219</v>
       </c>
       <c r="Q68" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="R68" t="n">
-        <v>16.1</v>
+        <v>15.78333333333333</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="B69" t="n">
-        <v>118000</v>
+        <v>82600</v>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D69" t="n">
-        <v>0.952803715659434</v>
+        <v>0.9404717494177394</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9602396443005726</v>
+        <v>0.9534168933777768</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9543466380200744</v>
+        <v>0.9465433619031904</v>
       </c>
       <c r="G69" t="n">
-        <v>0.9976174587374872</v>
+        <v>0.996917739194192</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9866984128857652</v>
+        <v>0.9806506380327612</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7686177070613659</v>
+        <v>0.7374622832505475</v>
       </c>
       <c r="J69" t="n">
-        <v>0.8730045755617194</v>
+        <v>0.8681177187724891</v>
       </c>
       <c r="K69" t="n">
-        <v>0.8405355209556622</v>
+        <v>0.8345566797132994</v>
       </c>
       <c r="L69" t="n">
-        <v>0.9407623864107668</v>
+        <v>0.9365206088218906</v>
       </c>
       <c r="M69" t="n">
-        <v>0.6592168673024401</v>
+        <v>0.654686421725951</v>
       </c>
       <c r="N69" t="n">
-        <v>0.8081744985823195</v>
+        <v>0.8036759564313963</v>
       </c>
       <c r="O69" t="n">
-        <v>0.7415921892723517</v>
+        <v>0.7377553068679817</v>
       </c>
       <c r="P69" t="n">
-        <v>0.8185302750043504</v>
+        <v>0.8132702785642024</v>
       </c>
       <c r="Q69" t="n">
         <v>51</v>
       </c>
       <c r="R69" t="n">
+        <v>16.65</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>70</v>
+      </c>
+      <c r="B70" t="n">
+        <v>82600</v>
+      </c>
+      <c r="C70" t="n">
+        <v>9</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.9536260865796208</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.958102016800561</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.9521045456719212</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.9974392185677866</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.9840803037923628</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.7341235636262003</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.873687938817852</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.842599741521999</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.9420602473079008</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.6600099622394273</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.8076694630404168</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.7424113619603053</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.8172829792937082</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>67</v>
+      </c>
+      <c r="R70" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="n">
+        <v>82600</v>
+      </c>
+      <c r="C71" t="n">
+        <v>10</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.9442477636356884</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.9556898854439824</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.9492422467405872</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.9965882825478708</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.9818009081802204</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.7714743664324838</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.8748139992039821</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.8424657150980922</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.9424423776641676</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.6555752891829719</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.8094835061870512</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.7379786309998486</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.8194722602448776</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>73</v>
+      </c>
+      <c r="R71" t="n">
+        <v>17.56666666666667</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>80</v>
+      </c>
+      <c r="B72" t="n">
+        <v>94400</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.9546663770384696</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.957081326397338</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.9502168207416494</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.997577313531962</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.9866359381095612</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.7556946090228501</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.8719982149943296</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.8374462382142496</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.9396507339510676</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.6602263995615884</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.8059202698421778</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.7407445548111533</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.8153886089175844</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>48</v>
+      </c>
+      <c r="R72" t="n">
+        <v>14.48333333333333</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>80</v>
+      </c>
+      <c r="B73" t="n">
+        <v>94400</v>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.9424942755042788</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.9513886797624066</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.9436952433181786</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.9972522236109028</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.984645820445304</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.7694087239010302</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.8735426415534479</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.8427287567496093</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.9414094534933368</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.6618580837175024</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.8082797621732033</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.7435750779575693</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.8178795524953089</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>66</v>
+      </c>
+      <c r="R73" t="n">
+        <v>18.36666666666667</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>80</v>
+      </c>
+      <c r="B74" t="n">
+        <v>94400</v>
+      </c>
+      <c r="C74" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.9411194273923644</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.9594305885386551</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.9538108076946986</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.997114703040744</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.9832307634406978</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.7716912045780399</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.8700569883724342</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.8380297406039905</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.9391556719398968</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.658409251457021</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.80797639733701</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.7391992522467585</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.8185612100085248</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>56</v>
+      </c>
+      <c r="R74" t="n">
+        <v>15.31666666666667</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>80</v>
+      </c>
+      <c r="B75" t="n">
+        <v>94400</v>
+      </c>
+      <c r="C75" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.9489018603627204</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.9535104267903139</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.9460612809842972</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.9972724560657312</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.9847909352872276</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.7581673316858651</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.8738146454082072</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.8392804035492261</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.9407270986600602</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6570876718101218</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.8071220145696771</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.7399602072278462</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.8177748628761639</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>65</v>
+      </c>
+      <c r="R75" t="n">
+        <v>16.71666666666667</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>80</v>
+      </c>
+      <c r="B76" t="n">
+        <v>94400</v>
+      </c>
+      <c r="C76" t="n">
+        <v>5</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.9397218752300536</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.9518526342978376</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.944560686862571</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.9965763544454054</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.9823168624012492</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.7562151573040093</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.8709856239952416</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.8348739119505788</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.938654981675015</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.6516676424737817</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.8039748422807005</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.7348208840343594</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.814729936654675</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>52</v>
+      </c>
+      <c r="R76" t="n">
+        <v>14.18333333333333</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>80</v>
+      </c>
+      <c r="B77" t="n">
+        <v>94400</v>
+      </c>
+      <c r="C77" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.9356291983233532</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.954337943763608</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.9477702211057863</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.9965328705234529</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.9817913734124299</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.771309286923576</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.8731585360783415</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.8405455371960827</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.94020599328905</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.6542075308042019</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.8078887191119754</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.7399658212273187</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.8177748683312027</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>66</v>
+      </c>
+      <c r="R77" t="n">
+        <v>17.95</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>80</v>
+      </c>
+      <c r="B78" t="n">
+        <v>94400</v>
+      </c>
+      <c r="C78" t="n">
+        <v>7</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.9484169512384232</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.956628840607007</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.94999664904235</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.9977331003940448</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.9858424598267368</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.7557035376395974</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.872120859472996</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.8396817491828032</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.9397557743255218</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.6596945170230167</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.809061510331918</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.7406338670040999</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.8202131116491798</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>50</v>
+      </c>
+      <c r="R78" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>80</v>
+      </c>
+      <c r="B79" t="n">
+        <v>94400</v>
+      </c>
+      <c r="C79" t="n">
+        <v>8</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.9539948354624465</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.9585791717744032</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.9524733231364032</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.9971406022022384</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.9846168196640416</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.740126144913808</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.8726974546056731</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.8373723257743713</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.93964230649106</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.6549250546321783</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.8075938069440012</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.7375054195511925</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.8179971891257771</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>56</v>
+      </c>
+      <c r="R79" t="n">
+        <v>19.88333333333333</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>80</v>
+      </c>
+      <c r="B80" t="n">
+        <v>94400</v>
+      </c>
+      <c r="C80" t="n">
+        <v>9</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.953948713603828</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.9590916220697806</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.9526459093043002</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.9976402790051442</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.9869182805915478</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.7680464136519645</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.874398591337241</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.8409402462875367</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.9416032635824898</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.6622879919739415</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.8092260691176055</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.7431541083424131</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.8195678854123452</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>53</v>
+      </c>
+      <c r="R80" t="n">
+        <v>15.35</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="n">
+        <v>94400</v>
+      </c>
+      <c r="C81" t="n">
+        <v>10</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.9528586967819686</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.9566698967145776</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.9499814038318606</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.9971852951495436</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.9833276951606882</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.7511655896445465</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.8732629451757826</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.8419750931418459</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.94083286905956</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.6611927426425023</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.8058192876203872</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.7418621733049384</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.8158883851524806</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>58</v>
+      </c>
+      <c r="R81" t="n">
+        <v>18.23333333333333</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>90</v>
+      </c>
+      <c r="B82" t="n">
+        <v>106200</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.9531955185514076</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.9636854727512968</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.9584891458362936</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.997493608820884</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.986279955434324</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.7683151533411842</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.8762759692884033</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.8423613271854093</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.9421739288535952</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.6583535421750554</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.8083586802871759</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.743621110989294</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.8186903687218439</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>56</v>
+      </c>
+      <c r="R82" t="n">
+        <v>16.06666666666667</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>90</v>
+      </c>
+      <c r="B83" t="n">
+        <v>106200</v>
+      </c>
+      <c r="C83" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.9469192111086738</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.9551608546973572</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.9485476208807176</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.9974129275844704</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.9845698917626264</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.7687400943204908</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.8689972744944023</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.8361838103755503</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.9376646658645432</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.6588145708512607</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.8050105893759524</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.7381659056277133</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0.8155866566130014</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>45</v>
+      </c>
+      <c r="R83" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>90</v>
+      </c>
+      <c r="B84" t="n">
+        <v>106200</v>
+      </c>
+      <c r="C84" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.9579818232250884</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.9632865992480208</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.9578208735507217</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.9979155358095236</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.9876369860899288</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.7615340800258081</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.8751961488924892</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.8430651501132558</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.9420133834052647</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.6613323351674056</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.8098157079701707</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.7427121718312089</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.8206530630887496</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>52</v>
+      </c>
+      <c r="R84" t="n">
+        <v>17.46666666666667</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>90</v>
+      </c>
+      <c r="B85" t="n">
+        <v>106200</v>
+      </c>
+      <c r="C85" t="n">
+        <v>4</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.9532049569333728</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.9546766025091176</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.9476246479199996</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.9966132182113084</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.984501495801418</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.7735815244546442</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.8745941072542824</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.8431710167500561</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.9423114762528432</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.6616089577629435</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.8104829243657274</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.7435834878506159</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0.8210178308723513</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>55</v>
+      </c>
+      <c r="R85" t="n">
+        <v>16.18333333333333</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>90</v>
+      </c>
+      <c r="B86" t="n">
+        <v>106200</v>
+      </c>
+      <c r="C86" t="n">
+        <v>5</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.9504529135702084</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.9587232135099436</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.9527897409436</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.997330969760432</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.9848811854136562</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.7568449273785216</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.8722448065903878</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.8392564274533871</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.9395916534218856</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.6590101574601378</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.8059289940531303</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.7393247225205706</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.8167159754420152</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>48</v>
+      </c>
+      <c r="R86" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>90</v>
+      </c>
+      <c r="B87" t="n">
+        <v>106200</v>
+      </c>
+      <c r="C87" t="n">
+        <v>6</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.952835755810804</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.9625114325988172</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.957129538124336</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.9973208972633356</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.9857055843429776</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.7531687696648588</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.8733310739789409</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.8413182433976796</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.9405744351762666</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.6624739464162389</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.8070805943811136</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.7418485188370584</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0.8170582477717524</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>50</v>
+      </c>
+      <c r="R87" t="n">
+        <v>14.81666666666667</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>90</v>
+      </c>
+      <c r="B88" t="n">
+        <v>106200</v>
+      </c>
+      <c r="C88" t="n">
+        <v>7</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.9414731441728204</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.9614971382152327</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.9560021026370134</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.9974852271788962</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.9846047656736912</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.7764478444427926</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.8707693205848035</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.8393455878046122</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.939340759203304</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.6596472564882703</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.8070912441760262</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.7403408944009082</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0.8168965375995043</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>58</v>
+      </c>
+      <c r="R88" t="n">
+        <v>17.43333333333333</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>90</v>
+      </c>
+      <c r="B89" t="n">
+        <v>106200</v>
+      </c>
+      <c r="C89" t="n">
+        <v>8</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.9547730854520596</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.9562174962291756</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.9491709598111024</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.9974146821263083</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.9867508543789782</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.719579257869241</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.8737014104200442</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.8376577392604028</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.9395753733175688</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.6550198548486522</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.8056135916668202</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.7396899308934084</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0.8158709268846394</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>46</v>
+      </c>
+      <c r="R89" t="n">
+        <v>17.71666666666667</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>90</v>
+      </c>
+      <c r="B90" t="n">
+        <v>106200</v>
+      </c>
+      <c r="C90" t="n">
+        <v>9</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.9503190279610758</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.9599502176738336</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.9540617570251138</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.9972637536699196</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.984144742338199</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.7614799336741446</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.8732513285047382</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.8427195811507544</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.94138191263529</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.6664870300095693</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.8069326625845524</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.7451038948588432</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0.8163582672753507</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>56</v>
+      </c>
+      <c r="R90" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="n">
+        <v>106200</v>
+      </c>
+      <c r="C91" t="n">
+        <v>10</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.9506238857852952</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.9574632837823738</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.9512920935344116</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.9973618319241174</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.983910473382744</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.7728440800239206</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.8696249393790735</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.8380864993180668</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.9389724694683892</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.6617568633812999</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.8030426389854319</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.7400764477822404</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.8118616921041248</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>56</v>
+      </c>
+      <c r="R91" t="n">
+        <v>19.76666666666667</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>100</v>
+      </c>
+      <c r="B92" t="n">
+        <v>118000</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.9514708777834512</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.9541599806109756</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.9471844988519482</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.9960358031375868</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.9810192240648744</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.7852531269396714</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.870669907746362</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.8383495495189892</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.9392158945854632</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.6575203635321591</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.8075862568927561</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.7368017654412373</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.8176647333656863</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>52</v>
+      </c>
+      <c r="R92" t="n">
+        <v>18.11666666666667</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>100</v>
+      </c>
+      <c r="B93" t="n">
+        <v>118000</v>
+      </c>
+      <c r="C93" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.955915774255244</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.960477275902818</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.9548526902997456</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.9974607783425116</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.9858744696137952</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.7390462201882121</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.8729358050742839</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.8383687442576484</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.9403738118222396</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.6588119869376617</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0.8071772707983176</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.7401098810032755</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0.8173234305099706</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>41</v>
+      </c>
+      <c r="R93" t="n">
+        <v>14.23333333333333</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>100</v>
+      </c>
+      <c r="B94" t="n">
+        <v>118000</v>
+      </c>
+      <c r="C94" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.9472369725599482</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.9597118205387848</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.9539495244885684</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.9973276594821128</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.984744103304552</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.7522940535459072</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.8700817860425122</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.8399263294110075</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.939455283837618</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.6606360166364864</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.8066930050414558</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.7419078497438281</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0.8170707624376189</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>52</v>
+      </c>
+      <c r="R94" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>100</v>
+      </c>
+      <c r="B95" t="n">
+        <v>118000</v>
+      </c>
+      <c r="C95" t="n">
+        <v>4</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.9412710564802362</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.958476662416502</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.9522730459344352</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.9974551300903688</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.9861103244306182</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.7472653187845248</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.8703936678523524</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.8388422145938996</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.9386725977844982</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.6565330016788367</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.8047120431249322</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.7375722411552172</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0.8142219303808694</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>50</v>
+      </c>
+      <c r="R95" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>100</v>
+      </c>
+      <c r="B96" t="n">
+        <v>118000</v>
+      </c>
+      <c r="C96" t="n">
+        <v>5</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.9514949544625052</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.9568749388752912</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.9501102797497194</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.9973468103816042</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.985005291448583</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.7517535218631746</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.8734997830242403</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.8409518335786538</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.9415155801244892</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.6631342121523356</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.807864609367937</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.743772850563051</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0.8172368854986581</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>48</v>
+      </c>
+      <c r="R96" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>100</v>
+      </c>
+      <c r="B97" t="n">
+        <v>118000</v>
+      </c>
+      <c r="C97" t="n">
+        <v>6</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.952803715659434</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.9602396443005726</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.9543466380200744</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.9976174587374872</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.9866984128857652</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.7686177070613659</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.8730045755617194</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.8405355209556622</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.9407623864107668</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.6592168673024401</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0.8081744985823195</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.7415921892723517</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.8185302750043504</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>51</v>
+      </c>
+      <c r="R97" t="n">
         <v>18.18333333333333</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>100</v>
+      </c>
+      <c r="B98" t="n">
+        <v>118000</v>
+      </c>
+      <c r="C98" t="n">
+        <v>7</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.9500376085520016</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9647914677611096</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.9600976118890272</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.9980041295295152</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.9870451885250155</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.7489797109432386</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.8738236615435786</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.8407462560125613</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.9411635725268304</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.6598628452447629</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0.8075607787712925</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.7420496539617647</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0.8177681828841449</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>48</v>
+      </c>
+      <c r="R98" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>100</v>
+      </c>
+      <c r="B99" t="n">
+        <v>118000</v>
+      </c>
+      <c r="C99" t="n">
+        <v>8</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.9490609899897652</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.9595454186520546</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.9534576796782978</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.9978448912974516</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.9876883321286936</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.7539282142250749</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.8749505498544879</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.8412540531055955</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.9418831501471444</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.659095607575455</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.8082525875448173</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.741167809227953</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0.8187575168827</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>45</v>
+      </c>
+      <c r="R99" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>100</v>
+      </c>
+      <c r="B100" t="n">
+        <v>118000</v>
+      </c>
+      <c r="C100" t="n">
+        <v>9</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.9436620216604114</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.958172594244169</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.9520464789934844</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.9969076950494036</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.9839707748340736</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.7756198047817793</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.8710908586703957</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.837894428835861</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.93954500587309</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.6554460282825838</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.804970503860075</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.7369549676903944</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.8146524757923663</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>46</v>
+      </c>
+      <c r="R100" t="n">
+        <v>15.65</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="n">
+        <v>118000</v>
+      </c>
+      <c r="C101" t="n">
+        <v>10</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.9550370675789857</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.9604690642447796</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.95489539408417</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.9975730822254342</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.9857259755848355</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.764013583293647</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.8734668517790539</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.838451253613403</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.9402738587601488</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.6549480986614667</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.8076477242150216</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.7393626445485726</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0.8187251202734622</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>51</v>
+      </c>
+      <c r="R101" t="n">
+        <v>17.01666666666667</v>
       </c>
     </row>
   </sheetData>
